--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -53,12 +53,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -67,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,28 +152,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -793,14 +787,14 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>19.9</v>
+      <c r="D4" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n">
@@ -815,20 +809,20 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="12" t="n">
-        <v>16</v>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>451.2</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0.1</v>
@@ -840,7 +834,7 @@
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
@@ -852,13 +846,13 @@
         <v>11</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -874,20 +868,20 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="11" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F5" s="11" t="n">
+      <c r="D5" s="9" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>42.5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>20.5</v>
@@ -901,15 +895,15 @@
       <c r="L5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>13.9</v>
+      <c r="M5" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>1.4</v>
@@ -918,28 +912,28 @@
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>90.5</v>
+        <v>0.5</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.2</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -957,14 +951,14 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>19.4</v>
+      <c r="D6" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.1</v>
@@ -976,38 +970,38 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>26.1</v>
+        <v>5.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R6" s="12" t="n">
-        <v>17.9</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1016,13 +1010,13 @@
         <v>2.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1038,29 +1032,29 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F7" s="11" t="n">
+        <v>255</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>41.2</v>
+      <c r="G7" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>24.4</v>
@@ -1068,44 +1062,44 @@
       <c r="M7" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="N7" s="12" t="n">
-        <v>67.09999999999999</v>
+      <c r="N7" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>17.2</v>
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X7" s="12" t="n">
-        <v>81.3</v>
+        <v>7</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1121,18 +1115,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>327.9</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G8" s="11" t="n">
+      <c r="E8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n"/>
@@ -1140,7 +1134,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1148,18 +1142,18 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="12" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>318.9</v>
+      <c r="M8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
+        <v>29.8</v>
       </c>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
+        <v>2.2</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.6</v>
@@ -1168,10 +1162,10 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>7.2</v>
+        <v>72</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>19.8</v>
@@ -1180,13 +1174,13 @@
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.2</v>
+        <v>10.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1202,17 +1196,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>16.5</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>7.4</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>11.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>61.5</v>
@@ -1221,18 +1215,18 @@
         <v>61.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1128.9</v>
+        <v>8.9</v>
       </c>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n">
-        <v>108.2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n">
@@ -1242,23 +1236,23 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>393.1</v>
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n">
-        <v>95.5</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>87.2</v>
+        <v>80.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>94.8</v>
+        <v>994.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>429</v>
+        <v>929</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>1.6</v>
@@ -1279,14 +1273,14 @@
       <c r="C10" s="3" t="n">
         <v>156.3</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="9" t="n">
         <v>165.1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="15" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="17" t="n">
-        <v>9.9</v>
+      <c r="F10" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>55</v>
@@ -1295,21 +1289,23 @@
         <v>61.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>74.3</v>
+        <v>29.3</v>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n">
-        <v>118.6</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.8</v>
@@ -1324,25 +1320,25 @@
         <v>44.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="12" t="n">
-        <v>91.40000000000001</v>
+      <c r="V10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="X10" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1360,22 +1356,22 @@
       <c r="C11" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>19.8</v>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
@@ -1387,16 +1383,16 @@
         <v>98.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="R11" s="12" t="n">
-        <v>81.7</v>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>89.5</v>
+        <v>9.5</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1.2</v>
@@ -1404,14 +1400,14 @@
       <c r="U11" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V11" s="12" t="n">
-        <v>18.6</v>
+      <c r="V11" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>20.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>1.1</v>
@@ -1431,20 +1427,20 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>41.8</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>10</v>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
@@ -1454,32 +1450,32 @@
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="12" t="n">
-        <v>78.90000000000001</v>
+      <c r="M12" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="12" t="n">
-        <v>17.9</v>
+        <v>0</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>14.9</v>
+        <v>0.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>858.9</v>
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.2</v>
@@ -1488,13 +1484,13 @@
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>93.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1510,16 +1506,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>19.8</v>
+      <c r="F13" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>13</v>
@@ -1528,34 +1524,34 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>23.8</v>
+        <v>20.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
@@ -1573,10 +1569,10 @@
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1593,16 +1589,16 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
-        <v>24.6</v>
+      <c r="D14" s="9" t="n">
+        <v>54.6</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="F14" s="16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G14" s="16" t="n">
+      <c r="F14" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1615,7 +1611,7 @@
         <v>2.8</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>12.5</v>
@@ -1624,11 +1620,11 @@
         <v>1.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>24.6</v>
@@ -1642,23 +1638,23 @@
       <c r="T14" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>20.6</v>
+      <c r="U14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1677,14 +1673,14 @@
       <c r="D15" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>19.1</v>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.1</v>
@@ -1693,10 +1689,10 @@
         <v>2.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>4.4</v>
@@ -1706,11 +1702,11 @@
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1719,10 +1715,10 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
@@ -1730,11 +1726,11 @@
       <c r="W15" s="3" t="n">
         <v>83.5</v>
       </c>
-      <c r="X15" s="12" t="n">
-        <v>88.59999999999999</v>
+      <c r="X15" s="8" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1753,41 +1749,41 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="15" t="n">
         <v>26.7</v>
       </c>
-      <c r="E16" s="17" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F16" s="17" t="n">
+      <c r="E16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="15" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>23.6</v>
+        <v>2.6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>481.9</v>
+        <v>8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>4.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>97.8</v>
+        <v>90</v>
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
@@ -1797,10 +1793,10 @@
         <v>1.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>55.8</v>
@@ -1809,10 +1805,10 @@
         <v>4094.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>20</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>41.1</v>
@@ -1834,14 +1830,14 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="9" t="n">
         <v>172.1</v>
       </c>
-      <c r="E17" s="16" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>19.1</v>
+      <c r="E17" s="9" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>62</v>
@@ -1853,25 +1849,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>66.2</v>
+        <v>60</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
@@ -1880,28 +1879,28 @@
         <v>46.1</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="U17" s="12" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>20.1</v>
+        <v>2.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>190.9</v>
+        <v>1.8</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>100.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>81.7</v>
+        <v>8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1917,23 +1916,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>9.800000000000001</v>
+      <c r="E18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.7</v>
@@ -1943,13 +1942,13 @@
       </c>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>998.6</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0</v>
@@ -1957,26 +1956,26 @@
       <c r="Q18" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="R18" s="12" t="n">
-        <v>19</v>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>742</v>
+        <v>10</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>15.1</v>
+        <v>10</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>63.2</v>
@@ -1998,14 +1997,14 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>19.9</v>
+      <c r="D19" s="9" t="n">
+        <v>142.51</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>9.6</v>
@@ -2014,11 +2013,11 @@
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n"/>
-      <c r="M19" s="12" t="n">
-        <v>14.9</v>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
@@ -2032,10 +2031,10 @@
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>13.4</v>
@@ -2047,10 +2046,10 @@
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2069,26 +2068,26 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>10.6</v>
+      <c r="D20" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
@@ -2097,16 +2096,16 @@
         <v>0.3</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>96.8</v>
+        <v>6</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>231.4</v>
@@ -2114,17 +2113,17 @@
       <c r="R20" s="3" t="n">
         <v>115.1</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>91.2</v>
+        <v>2</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>42.2</v>
@@ -2133,10 +2132,10 @@
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2152,17 +2151,17 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>19.8</v>
+      <c r="D21" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n">
@@ -2172,52 +2171,52 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.3</v>
+        <v>10</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2233,26 +2232,26 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>90.59999999999999</v>
+      <c r="E22" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>5.1</v>
@@ -2261,44 +2260,44 @@
         <v>16.5</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>16.3</v>
+        <v>0.3</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1188.8</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n">
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>99.8</v>
+        <v>29</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>12.7</v>
+        <v>1.3</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>161.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2316,20 +2315,20 @@
       <c r="C23" s="3" t="n">
         <v>128.2</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="15" t="n">
         <v>25.8</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>12.7</v>
+      <c r="E23" s="15" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>10.7</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>61.4</v>
+        <v>1.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53.9</v>
+        <v>53</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>2.5</v>
@@ -2338,45 +2337,45 @@
         <v>3.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>43.2</v>
       </c>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>115.6</v>
+        <v>53.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
+        <v>1.5</v>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n">
         <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>219.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>94.3</v>
+        <v>9.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>86.3</v>
+        <v>80</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>76.7</v>
@@ -2395,44 +2394,44 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="15" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="16" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>97.5</v>
+      <c r="E24" s="9" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="12" t="n">
-        <v>1.7</v>
+      <c r="L24" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R24" s="12" t="n">
-        <v>18.3</v>
+        <v>2.3</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.9</v>
@@ -2443,20 +2442,20 @@
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="12" t="n">
-        <v>89.40000000000001</v>
+      <c r="V24" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X24" s="12" t="n">
-        <v>17.8</v>
+        <v>0</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2476,9 +2475,9 @@
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F25" s="16" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>1.3</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2488,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>22</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.1</v>
@@ -2500,22 +2499,22 @@
         <v>1.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">0 0
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="Q25" s="12" t="n">
-        <v>1156.1</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>1.2</v>
@@ -2524,16 +2523,18 @@
         <v>0.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X25" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="3" t="n">
         <v>95</v>
       </c>
@@ -2554,22 +2555,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>22.8</v>
+        <v>1.2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>19.3</v>
+        <v>13.5</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n">
@@ -2585,38 +2586,38 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="W26" s="12" t="n">
-        <v>15.3</v>
+        <v>10.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2644,10 +2645,10 @@
       </c>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>4.3</v>
@@ -2657,16 +2658,16 @@
         <v>15.8</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N27" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P27" s="12" t="n">
-        <v>12.8</v>
+        <v>20</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>18</v>
@@ -2675,13 +2676,13 @@
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>19</v>
@@ -2690,13 +2691,13 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>21.8</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2712,14 +2713,14 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>18.5</v>
+      <c r="E28" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
@@ -2735,32 +2736,32 @@
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="12" t="n">
-        <v>19.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>2</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2769,10 +2770,10 @@
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>99.8</v>
+        <v>10</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.9</v>
@@ -2794,18 +2795,18 @@
       <c r="D29" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F29" s="16" t="n">
-        <v>81.7</v>
+      <c r="F29" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.6</v>
@@ -2820,40 +2821,40 @@
         <v>44.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>434.3</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>19</v>
+      <c r="R29" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W29" s="12" t="n">
-        <v>31</v>
+        <v>0.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.2</v>
+        <v>9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2872,20 +2873,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1116.8</v>
-      </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>18.5</v>
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>8.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.8</v>
@@ -2895,40 +2898,40 @@
       </c>
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>199.8</v>
+        <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4213.8</v>
+        <v>1.3</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>21.8</v>
+        <v>1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>1.3</v>
@@ -2953,20 +2956,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="15" t="n">
         <v>14.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>3.9</v>
@@ -2975,48 +2980,48 @@
         <v>2.5</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>20</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>74.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>7058</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="W31" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>92.09999999999999</v>
+      <c r="W31" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3032,31 +3037,28 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144 1
-</t>
-        </is>
+      <c r="E32" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
@@ -3066,47 +3068,44 @@
         <v>14.9</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.2</v>
+        <v>12</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>180.9</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R32" s="12" t="n">
+      <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="V32" s="3" t="n"/>
-      <c r="W32" s="12" t="n">
-        <v>16.2</v>
+      <c r="W32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">0 0 0
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 13
-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3122,22 +3121,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>90.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="9" t="n">
         <v>81.33</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>14.3</v>
+      <c r="G33" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.3</v>
@@ -3147,32 +3146,32 @@
         <v>39.1</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>7</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>17.8</v>
@@ -3181,13 +3180,13 @@
         <v>6.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>89.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3203,17 +3202,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="12" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F34" s="16" t="n">
+      <c r="D34" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>81.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.4</v>
@@ -3223,36 +3222,36 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>14.2</v>
+        <v>0</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n"/>
       <c r="P34" s="3" t="n">
-        <v>10.6</v>
+        <v>20</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n">
-        <v>17.3</v>
+        <v>10</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96.8</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>16.4</v>
+        <v>0.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>52.2</v>
@@ -3264,7 +3263,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3280,72 +3279,72 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>14.2</v>
+      <c r="E35" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>15.1</v>
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q35" s="12" t="n">
-        <v>76.90000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>15.9</v>
+        <v>10</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="W35" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X35" s="12" t="n">
-        <v>86.59999999999999</v>
+      <c r="W35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>218.6</v>
+        <v>0.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3364,14 +3363,14 @@
       <c r="D36" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
+      <c r="F36" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
@@ -3383,23 +3382,23 @@
         <v>4.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1</v>
+        <v>7</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="12" t="n">
-        <v>66.40000000000001</v>
+      <c r="N36" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>28.9</v>
+        <v>3</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>1.4</v>
@@ -3408,10 +3407,10 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>10</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
@@ -3420,13 +3419,13 @@
         <v>2.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3442,45 +3441,50 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="17" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E37" s="17" t="n">
+      <c r="D37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <v>13.8</v>
       </c>
-      <c r="F37" s="17" t="n">
-        <v>19.5</v>
+      <c r="F37" s="15" t="n">
+        <v>0.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 0
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>13.3</v>
+        <v>3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.1</v>
+        <v>0.7</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>987.8</v>
+        <v>20</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>89.90000000000001</v>
@@ -3496,7 +3500,7 @@
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>7.6</v>
@@ -3505,7 +3509,7 @@
         <v>42.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3521,53 +3525,53 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="9" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="16" t="n">
-        <v>92.2</v>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n">
-        <v>56.9</v>
+        <v>50.9</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>81.3</v>
+      <c r="L38" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>492</v>
+        <v>90</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q38" s="12" t="n">
-        <v>18</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>90</v>
@@ -3579,10 +3583,10 @@
         <v>126.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>185.9</v>
+        <v>5.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3600,72 +3604,72 @@
       <c r="C39" s="3" t="n">
         <v>44.3</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>18.4</v>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>11.3</v>
+        <v>0.1</v>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>13.7</v>
+      <c r="L39" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>15.4</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P39" s="12" t="n">
-        <v>8.4</v>
+        <v>9</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="12" t="n">
-        <v>81</v>
+      <c r="V39" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3681,74 +3685,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>637.7</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E40" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E40" s="13" t="n">
         <v>11.1</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>18.5</v>
+      <c r="F40" s="13" t="n">
+        <v>23.5</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16.3</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>17.6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>41.3</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>92.2</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P40" s="3" t="n"/>
       <c r="Q40" s="3" t="n">
-        <v>24.8</v>
+        <v>29.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>85.8</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>62.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>116.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3764,19 +3768,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>408.8</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D41" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="E41" s="11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F41" s="11" t="n">
+      <c r="E41" s="13" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F41" s="13" t="n">
         <v>17.9</v>
       </c>
-      <c r="G41" s="11" t="n">
-        <v>16.2</v>
+      <c r="G41" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>34.7</v>
@@ -3791,31 +3795,31 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>1.3</v>
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>1</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
@@ -3827,13 +3831,13 @@
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39.8</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3849,23 +3853,23 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E42" s="13" t="n"/>
+        <v>60.9</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.1</v>
@@ -3874,34 +3878,34 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>12.3</v>
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>920</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>25.2</v>
+        <v>20</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>49.8</v>
+        <v>99</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
@@ -3913,10 +3917,10 @@
         <v>0.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3932,79 +3936,82 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>1.7</v>
+        <v>5</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">00000 0
 </t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>0.5</v>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="I43" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>12.2</v>
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>90</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S43" s="12" t="n">
-        <v>61.8</v>
+      <c r="S43" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <v>18.9</v>
+        <v>10</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>20.5</v>
+        <v>5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4020,76 +4027,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3119.5</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>1.7</v>
+        <v>3109.5</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">00000 0
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>0.5</v>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="I44" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>5002</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>12.2</v>
+        <v>0</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>10110110.1</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S44" s="12" t="n">
-        <v>11</v>
+        <v>20.8</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>150115100011.5</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V44" s="12" t="n">
-        <v>1989.8</v>
+        <v>0</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>2.2</v>
@@ -4108,43 +4118,43 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3119.5</v>
-      </c>
-      <c r="D45" s="17" t="n">
+        <v>3109.5</v>
+      </c>
+      <c r="D45" s="15" t="n">
         <v>31.3</v>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="15" t="n">
         <v>53.4</v>
       </c>
-      <c r="F45" s="17" t="n">
-        <v>92.5</v>
+      <c r="F45" s="15" t="n">
+        <v>22.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
+        <v>56.9</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>53.1</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>621.9</v>
+        <v>60.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>498</v>
+        <v>90</v>
       </c>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
@@ -4154,25 +4164,25 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2929.8</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>729.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>108.9</v>
+        <v>1208.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>328.8</v>
+        <v>300.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>2.2</v>
@@ -4193,16 +4203,16 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F46" s="11" t="n">
+      <c r="D46" s="15" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F46" s="15" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4217,47 +4227,47 @@
       <c r="K46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>11.1</v>
+      <c r="L46" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>13.1</v>
+        <v>0.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="P46" s="12" t="n">
-        <v>4.4</v>
+        <v>9</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.3</v>
+        <v>1.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U46" s="12" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>8.9</v>
+        <v>50</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>208.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -41,8 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,20 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,16 +152,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,7 +173,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -786,73 +792,73 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
+        <v>289.1</v>
+      </c>
       <c r="D4" s="9" t="n">
-        <v>2.5</v>
+        <v>25.9</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>3.8</v>
+        <v>13.9</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>1</v>
+      <c r="I4" s="15" t="n">
+        <v>10.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
+        <v>27.8</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>451.2</v>
+        <v>13.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q4" s="15" t="n">
+        <v>266.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>3.3</v>
+        <v>21.1</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>11</v>
+        <v>43.2</v>
+      </c>
+      <c r="W4" s="15" t="n">
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>10.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -867,73 +873,75 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>1564.3</v>
+      </c>
       <c r="D5" s="9" t="n">
-        <v>26.51</v>
+        <v>25.5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>20.3</v>
+        <v>15.5</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>20.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>3.5</v>
+      <c r="H5" s="15" t="n">
+        <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N5" s="3" t="n"/>
+      <c r="L5" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R5" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R5" s="15" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5</v>
+        <v>20.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>94.8</v>
+        <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>17.9</v>
+        <v>20.3</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>10</v>
+        <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>10</v>
+        <v>293</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -951,72 +959,72 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>9</v>
+      <c r="D6" s="9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>19.3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
+      <c r="H6" s="15" t="n">
+        <v>1141.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>22</v>
+      <c r="M6" s="15" t="n">
+        <v>994.2</v>
+      </c>
+      <c r="N6" s="15" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>10.1</v>
+        <v>44.4</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62</v>
+        <v>671.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1</v>
+        <v>1103.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1032,74 +1040,70 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255</v>
+        <v>355.7</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F7" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>10.7</v>
+      <c r="G7" s="15" t="n">
+        <v>80.09999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>24.4</v>
+        <v>41.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>4.2</v>
+        <v>52.2</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>298.5</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>41.1</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.9</v>
+        <v>9.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>18.8</v>
+        <v>12.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,72 +1119,72 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+        <v>19.6</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>441.2</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>31</v>
+        <v>5.2</v>
+      </c>
+      <c r="M8" s="15" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>4971.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="P8" s="3" t="n"/>
+        <v>99.8</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R8" s="15" t="n">
         <v>18.6</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="V8" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V8" s="15" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>17.8</v>
+      <c r="W8" s="15" t="n">
+        <v>917.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>10.2</v>
+        <v>19.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1195,40 +1199,44 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>11.9</v>
+      <c r="C9" s="3" t="n">
+        <v>182528.1</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.5</v>
+        <v>161.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>61.6</v>
+        <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K9" s="3" t="n"/>
+        <v>21.7</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>28.9</v>
+      </c>
       <c r="L9" s="3" t="n">
-        <v>4.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N9" s="3" t="n"/>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="n">
         <v>103.3</v>
       </c>
@@ -1236,26 +1244,26 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.6</v>
+        <v>195.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>393.1</v>
-      </c>
-      <c r="U9" s="3" t="n"/>
+        <v>998.8</v>
+      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="n">
-        <v>0</v>
+        <v>295.3</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>80.2</v>
+        <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>994.8</v>
+        <v>194.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>929</v>
+        <v>19429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1271,45 +1279,39 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>156.3</v>
+        <v>365</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>165.1</v>
-      </c>
-      <c r="E10" s="15" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>61.5</v>
-      </c>
+      <c r="F10" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="M10" s="15" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -1317,28 +1319,22 @@
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>44.1</v>
+        <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X10" s="8" t="n">
-        <v>10</v>
+        <v>19.1</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>9</v>
+        <v>38.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1354,65 +1350,69 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="3" t="n">
+        <v>329.6</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H11" s="15" t="n">
         <v>10.7</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>1.7</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N11" s="3" t="n"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="15" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O11" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>9.5</v>
+        <v>92.8</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q11" s="15" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R11" s="15" t="n">
+        <v>811.4</v>
+      </c>
+      <c r="S11" s="15" t="n">
+        <v>289.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.2</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="15" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W11" s="15" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X11" s="15" t="n">
+        <v>20.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>98.8</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1427,70 +1427,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="9" t="n">
-        <v>0</v>
+        <v>521.2</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>4.1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>41.8</v>
+        <v>41.3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>22.2</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>12</v>
+      <c r="M12" s="15" t="n">
+        <v>24.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99</v>
+        <v>299.9</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>0.9</v>
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="15" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S12" s="15" t="n">
+        <v>46.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>188.6</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V12" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="V12" s="15" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1506,58 +1512,58 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>9455.6</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F13" s="9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>4.4</v>
+        <v>41.1</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>717.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>10.8</v>
+        <v>13.3</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>20.8</v>
+        <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>66.8</v>
+        <v>166.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1566,15 +1572,17 @@
         <v>20.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="Z13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1588,46 +1596,50 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="9" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>11.4</v>
+      <c r="C14" s="3" t="n">
+        <v>20319.9</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>44.1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="I14" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.7</v>
-      </c>
       <c r="L14" s="3" t="n">
-        <v>12.5</v>
+        <v>43.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>820.2</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>929</v>
+      </c>
       <c r="P14" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>18.8</v>
@@ -1635,26 +1647,22 @@
       <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="15" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="W14" s="15" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1669,44 +1677,44 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>484.5</v>
+      </c>
       <c r="D15" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0</v>
+        <v>26.7</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="G15" s="15" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P15" s="15" t="n">
         <v>1.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>23</v>
+        <v>2.1</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1715,25 +1723,21 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>948</v>
+      </c>
+      <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>80.59999999999999</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>89</v>
+        <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.6</v>
+        <v>31.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1748,73 +1752,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="15" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2.6</v>
+      <c r="C16" s="3" t="n">
+        <v>2326.9</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>16.2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>195481.9</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>3</v>
+        <v>113.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0</v>
+        <v>166.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>4.1</v>
+        <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>19491</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="Q16" s="3" t="n">
         <v>115.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.8</v>
+        <v>5.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>4094.8</v>
+        <v>10</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>20</v>
+        <v>190.9</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>41.1</v>
+        <v>929</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1829,78 +1835,73 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="9" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>62</v>
+      <c r="C17" s="3" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>82.40000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="15" t="n">
         <v>13.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00 0
-</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="M17" s="15" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="S17" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S17" s="15" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>0</v>
+        <v>562.6</v>
+      </c>
+      <c r="U17" s="15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="15" t="n">
+        <v>1.4</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>100.9</v>
+        <v>18.2</v>
+      </c>
+      <c r="X17" s="15" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>898</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8</v>
+        <v>297.4</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1915,73 +1916,67 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="8" t="n">
-        <v>13</v>
+      <c r="C18" s="3" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>23.9</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>2.7</v>
-      </c>
+        <v>19.1</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>18.3</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="15" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R18" s="15" t="n">
+        <v>719</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="V18" s="15" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="W18" s="15" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>10</v>
+        <v>16.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>63.2</v>
+        <v>6.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1996,31 +1991,39 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
+        <v>435.6</v>
+      </c>
       <c r="D19" s="9" t="n">
-        <v>142.51</v>
+        <v>22.4</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>16.2</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+        <v>12.7</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M19" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>196.8</v>
+      </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
@@ -2031,25 +2034,23 @@
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>10.9</v>
+        <v>13.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="W19" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="15" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W19" s="15" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>89</v>
+        <v>894.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2067,75 +2068,67 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0.6</v>
+      <c r="C20" s="3" t="n">
+        <v>494.9</v>
+      </c>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="13" t="n">
+        <v>124.94</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>18.1</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.3</v>
+        <v>12.6</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>10.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>231.4</v>
+        <v>221.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="S20" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S20" s="15" t="n">
         <v>16.7</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>28</v>
-      </c>
+      <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0.2</v>
+        <v>19.2</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>42.2</v>
+        <v>43.4</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="Y20" s="3" t="n">
-        <v>80</v>
-      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
       <c r="Z20" s="3" t="n">
-        <v>2</v>
+        <v>21.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2150,74 +2143,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>379.3</v>
+      </c>
       <c r="D21" s="3" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n">
-        <v>0.3</v>
+        <v>25.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>88.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.3</v>
+        <v>12.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N21" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
+        <v>19.3</v>
+      </c>
+      <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>16.5</v>
+        <v>94.7</v>
+      </c>
+      <c r="V21" s="15" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W21" s="15" t="n">
+        <v>169.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>18.6</v>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2231,74 +2220,70 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
-        <v>25.4</v>
+      <c r="C22" s="3" t="n">
+        <v>508.9</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>45.8</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F22" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M22" s="15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P22" s="15" t="n">
         <v>1.6</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="R22" s="3" t="n">
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="15" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>10</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>29</v>
+        <v>9.4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V22" s="15" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20</v>
+        <v>36.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z22" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2313,72 +2298,74 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>1.9</v>
+        <v>2089.4</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>1128.5</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>116.1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.5</v>
+        <v>110.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>115.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>20.5</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>22</v>
+        <v>29489</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>53.6</v>
+        <v>1113.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S23" s="3" t="n"/>
+        <v>14.5</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>191.8</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>328</v>
+        <v>2328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1219.8</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>9.4</v>
+        <v>194.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>80</v>
+        <v>186.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>9429</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>76.7</v>
+        <v>116.9</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2393,70 +2380,64 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="15" t="n">
+      <c r="C24" s="3" t="n">
+        <v>43791.8</v>
+      </c>
+      <c r="D24" s="16" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="8" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="E24" s="16" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr"/>
+      <c r="G24" s="13" t="n">
+        <v>2156.6</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="n"/>
+        <v>4.4</v>
+      </c>
+      <c r="M24" s="15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
+        <v>97.8</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q24" s="15" t="n">
+        <v>39.9</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="8" t="n">
-        <v>10.8</v>
+      <c r="V24" s="15" t="n">
+        <v>189.4</v>
+      </c>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="15" t="n">
+        <v>8881.200000000001</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
-      <c r="Z24" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2470,76 +2451,71 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
+        <v>233.6</v>
+      </c>
       <c r="D25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>0</v>
+      <c r="E25" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
+        <v>10.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 0
-</t>
-        </is>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>198</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>1.2</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q25" s="15" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R25" s="15" t="n">
+        <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.9</v>
+        <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="U25" s="3" t="n"/>
+        <v>111.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="W25" s="3" t="inlineStr"/>
       <c r="X25" s="3" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2555,71 +2531,73 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="15" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M26" s="15" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n"/>
+      <c r="P26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="R26" s="3" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>3</v>
+        <v>931.8</v>
       </c>
       <c r="U26" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="W26" s="15" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2633,71 +2611,69 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C27" s="3" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n">
-        <v>15.8</v>
+        <v>1.6</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="15" t="n">
+        <v>183.5</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>0</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>18</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q27" s="15" t="n">
+        <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.1</v>
+        <v>28.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="15" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="X27" s="3" t="inlineStr"/>
       <c r="Y27" s="3" t="n">
-        <v>28</v>
+        <v>88.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2712,71 +2688,71 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n">
+      <c r="C28" s="3" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="D28" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G28" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I28" s="3" t="n"/>
+      <c r="H28" s="15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K28" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K28" s="15" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3" t="n"/>
+        <v>44.5</v>
+      </c>
+      <c r="M28" s="15" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>0.8</v>
+        <v>98</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="15" t="n">
+        <v>19.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2</v>
+        <v>42.2</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>10</v>
+        <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17</v>
+        <v>41.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2791,70 +2767,68 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>309.1</v>
+      </c>
       <c r="D29" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="E29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="15" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>44.5</v>
+        <v>13.1</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>82.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>99</v>
+        <v>991</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>434.3</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>10.9</v>
-      </c>
+        <v>23.6</v>
+      </c>
+      <c r="R29" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>856.1</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V29" s="15" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="W29" s="15" t="n">
+        <v>1991</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>9</v>
+        <v>17.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2873,71 +2847,67 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G30" s="3" t="n">
+        <v>1569.9</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>1629.4</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="n">
+        <v>444924.4</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>212.1</v>
+      </c>
+      <c r="Q30" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="H30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>23.6</v>
-      </c>
       <c r="R30" s="3" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1.3</v>
+        <v>9413.799999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1</v>
+        <v>244.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85</v>
+        <v>185.9</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>182.9</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>4250.1</v>
+        <v>922</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>4.4</v>
@@ -2956,72 +2926,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>23.9</v>
+        <v>314</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="H31" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3" t="n"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>7058</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>8115.4</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>4.6</v>
+      <c r="W31" s="15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3037,76 +3005,61 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>282.13</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="L32" s="15" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M32" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>14.9</v>
-      </c>
       <c r="N32" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="R32" s="15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 0 0
-</t>
-        </is>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3121,72 +3074,70 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>22.8</v>
+        <v>411.2</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>23.1</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>1.4</v>
+        <v>13.7</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>81.33</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>19</v>
+        <v>18.4</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
+        <v>11.5</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="K33" s="3" t="n">
-        <v>39.1</v>
+        <v>2.2</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
+        <v>14.3</v>
+      </c>
+      <c r="M33" s="15" t="n">
+        <v>1097.2</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>20</v>
+        <v>99.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="15" t="n">
+        <v>191.2</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>0.6</v>
+        <v>16.4</v>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="15" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
+      </c>
+      <c r="X33" s="15" t="n">
+        <v>980</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>20</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.8</v>
+        <v>12.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3201,69 +3152,69 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>1144.4</v>
+      </c>
       <c r="D34" s="9" t="n">
-        <v>0.7</v>
+        <v>19.7</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>3.7</v>
+        <v>15.1</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>81.7</v>
+        <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I34" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>10</v>
-      </c>
+        <v>15.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="3" t="n"/>
+        <v>18.8</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>299</v>
+      </c>
       <c r="P34" s="3" t="n">
-        <v>20</v>
+        <v>18.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>90</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>0.4</v>
+        <v>21</v>
+      </c>
+      <c r="V34" s="15" t="n">
+        <v>16.9</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>18</v>
+        <v>43.2</v>
+      </c>
+      <c r="X34" s="15" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3278,73 +3229,75 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>477.8</v>
+      </c>
       <c r="D35" s="9" t="n">
-        <v>41.6</v>
+        <v>24.1</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>1.5</v>
+        <v>12.1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>1.2</v>
+        <v>18.1</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>30.9</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="M35" s="15" t="n">
+        <v>21281.8</v>
+      </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>15</v>
+        <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18</v>
+        <v>23.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>60</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="T35" s="3" t="inlineStr"/>
       <c r="U35" s="3" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>5</v>
+        <v>48.4</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>6.5</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>89</v>
+        <v>284</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3359,73 +3312,73 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>613.2</v>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F36" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="L36" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>3</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q36" s="15" t="n">
+        <v>27</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="S36" s="15" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
       <c r="U36" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V36" s="15" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>12.6</v>
+        <v>41.2</v>
+      </c>
+      <c r="X36" s="15" t="n">
+        <v>32.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3440,76 +3393,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>0.5</v>
+      <c r="C37" s="3" t="n">
+        <v>19782.4</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>1092.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 0
-</t>
-        </is>
+        <v>32.8</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>56.9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.7</v>
+        <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>150.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>10</v>
+        <v>1681.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>19.6</v>
+        <v>167.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20</v>
+        <v>9492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>9</v>
+        <v>401.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>189.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3819.1</v>
+        <v>382191.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V37" s="3" t="n"/>
+        <v>233.2</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="W37" s="3" t="n">
-        <v>1</v>
+        <v>181.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7.6</v>
+        <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3524,69 +3478,69 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="9" t="n">
-        <v>484.1</v>
-      </c>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="C38" s="3" t="n">
+        <v>495.6</v>
+      </c>
+      <c r="D38" s="17" t="inlineStr"/>
+      <c r="E38" s="13" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J38" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
       <c r="M38" s="3" t="n">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R38" s="3" t="n"/>
-      <c r="S38" s="3" t="n">
-        <v>12.6</v>
+        <v>30.2</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S38" s="15" t="n">
+        <v>172</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
-      <c r="U38" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U38" s="15" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="V38" s="15" t="n">
+        <v>8101.4</v>
+      </c>
+      <c r="W38" s="3" t="inlineStr"/>
       <c r="X38" s="3" t="n">
-        <v>126.1</v>
+        <v>17.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>5.9</v>
+        <v>184.6</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3602,74 +3556,68 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>44.3</v>
+        <v>624.3</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I39" s="3" t="n"/>
+        <v>17.6</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.9</v>
+        <v>8</v>
+      </c>
+      <c r="L39" s="15" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="15" t="n">
+        <v>2120.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="P39" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q39" s="15" t="n">
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>15.5</v>
+        <v>18.9</v>
+      </c>
+      <c r="S39" s="15" t="n">
+        <v>50.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>16</v>
+        <v>12.8</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="15" t="n">
+        <v>98.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>67</v>
+        <v>162.8</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3685,74 +3633,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="E40" s="13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>637.7</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>41.3</v>
+        <v>10</v>
+      </c>
+      <c r="L40" s="15" t="n">
+        <v>110</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>2</v>
+        <v>19.8</v>
+      </c>
+      <c r="N40" s="15" t="n">
+        <v>21.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n">
-        <v>29.8</v>
+        <v>98</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q40" s="15" t="n">
+        <v>35.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>16.7</v>
+      </c>
+      <c r="V40" s="15" t="n">
+        <v>22.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>6.9</v>
+        <v>3.1</v>
+      </c>
+      <c r="X40" s="15" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0.8</v>
+        <v>59</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0.8</v>
+        <v>26.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3768,76 +3716,68 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>794.3</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
+      </c>
+      <c r="M41" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N41" s="15" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="15" t="n">
+        <v>1.9</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>25.2</v>
+      </c>
+      <c r="R41" s="3" t="inlineStr"/>
       <c r="S41" s="3" t="n">
-        <v>0.9</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W41" s="15" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>0</v>
+      <c r="X41" s="15" t="n">
+        <v>22.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3853,74 +3793,72 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>60.9</v>
+        <v>608.8</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I42" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" s="3" t="n">
-        <v>5.1</v>
+        <v>35.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>920</v>
-      </c>
+        <v>93.2</v>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
       <c r="P42" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>20</v>
+        <v>26.9</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>0.9</v>
+        <v>16.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>99</v>
+        <v>949</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="15" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>0.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0</v>
+        <v>161.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10</v>
+        <v>18.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3936,82 +3874,70 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>2.9</v>
+        <v>604.4</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00000 0
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00 0
-</t>
-        </is>
+        <v>19.2</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>81</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>3.5</v>
+        <v>23.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="K43" s="15" t="n">
+        <v>8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0.5</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="n">
-        <v>20.8</v>
+        <v>24.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="T43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>0.6</v>
-      </c>
       <c r="X43" s="3" t="n">
-        <v>10.9</v>
+        <v>15.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0</v>
+        <v>729.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>5</v>
+        <v>20.3</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4026,84 +3952,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>3109.5</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00000 0
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00 0
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>2.2</v>
-      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="14" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4118,74 +3990,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3109.5</v>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>22.5</v>
+        <v>3119.5</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>72.5</v>
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>18.9</v>
+        <v>1181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.9</v>
+        <v>356.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>53.1</v>
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>60.9</v>
+        <v>168.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>496</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>124.8</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>126.3</v>
+        <v>1126.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>0</v>
+        <v>1282.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>729.8</v>
+        <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1208.9</v>
+        <v>1108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>0</v>
+        <v>1060.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>300.8</v>
+        <v>23028.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2.2</v>
+        <v>20.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4203,73 +4077,63 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="15" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>15.5</v>
+      <c r="D46" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>50.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>1</v>
+        <v>13.8</v>
+      </c>
+      <c r="J46" s="15" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="15" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="M46" s="15" t="n">
+        <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>13.9</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q46" s="15" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="R46" s="15" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>208.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>8.699999999999999</v>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="15" t="n">
+        <v>865.4</v>
+      </c>
+      <c r="V46" s="15" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W46" s="15" t="n">
+        <v>16.6</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,25 +146,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,48 +786,50 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
+      <c r="G4" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H4" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="15" t="n">
-        <v>10.8</v>
+      <c r="I4" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="L4" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="L4" s="14" t="n">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99.8</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q4" s="15" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>21.1</v>
+      <c r="P4" s="14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Q4" s="14" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R4" s="14" t="n">
+        <v>89.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
@@ -844,21 +837,23 @@
       <c r="T4" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="V4" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="W4" s="15" t="n">
-        <v>17</v>
+        <v>17.8</v>
+      </c>
+      <c r="W4" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>4.6</v>
+        <v>10.9</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -874,33 +869,33 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1564.3</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F5" s="9" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>20.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="H5" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H5" s="14" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -910,13 +905,15 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>95.8</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="15" t="n">
+      <c r="R5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -929,19 +926,19 @@
         <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="W5" s="15" t="n">
-        <v>17.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="W5" s="14" t="n">
+        <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -960,71 +957,73 @@
         <v>338</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>19.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>1141.6</v>
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>110.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M6" s="15" t="n">
-        <v>994.2</v>
-      </c>
-      <c r="N6" s="15" t="n">
-        <v>16.1</v>
+        <v>14.5</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>21562.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>1.9</v>
+        <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>44.4</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>671.8</v>
+        <v>62.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.2</v>
+        <v>18.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1103.9</v>
+        <v>1.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1040,52 +1039,56 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>355.7</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F7" s="9" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F7" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>80.09999999999999</v>
+      <c r="G7" s="11" t="n">
+        <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.3</v>
+        <v>11.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>41.4</v>
+        <v>19.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>52.2</v>
+        <v>15.2</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>298.5</v>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="S7" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T7" s="3" t="n">
         <v>77</v>
       </c>
@@ -1093,14 +1096,16 @@
         <v>9.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>184</v>
+        <v>8.4</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.5</v>
@@ -1119,72 +1124,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.9</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F8" s="9" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="H8" s="3" t="n">
-        <v>441.2</v>
+        <v>14.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>14.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M8" s="15" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N8" s="15" t="n">
-        <v>4971.2</v>
+      <c r="L8" s="14" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>31.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>99.8</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R8" s="15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T8" s="3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W8" s="15" t="n">
-        <v>917.8</v>
+      <c r="V8" s="14" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>97.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1200,70 +1209,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182528.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>126</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="F9" s="9" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>161.5</v>
+        <v>61.5</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>21.7</v>
+        <v>19.7</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>28.9</v>
+        <v>1281.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
+        <v>423.8</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>103.3</v>
+        <v>10.3</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>195.6</v>
+        <v>985.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>998.8</v>
-      </c>
-      <c r="U9" s="3" t="inlineStr"/>
+        <v>910.1</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>295.3</v>
+        <v>95.5</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>194.8</v>
+        <v>949.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>19429</v>
+        <v>94290.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1279,41 +1294,49 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="D10" s="9" t="n">
+        <v>3650.1</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="11" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="G10" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>41.2</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>16.8</v>
+        <v>11.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="n">
+        <v>83.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>18</v>
@@ -1324,17 +1347,23 @@
       <c r="T10" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W10" s="14" t="n">
+        <v>17.4</v>
+      </c>
       <c r="X10" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>85.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>38.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1355,64 +1384,72 @@
       <c r="D11" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="E11" s="9" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>13.9</v>
+      </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="15" t="n">
-        <v>1.6</v>
+        <v>11.7</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="P11" s="15" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="Q11" s="15" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R11" s="15" t="n">
-        <v>811.4</v>
-      </c>
-      <c r="S11" s="15" t="n">
-        <v>289.5</v>
+        <v>91.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="Q11" s="14" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V11" s="15" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W11" s="15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V11" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W11" s="14" t="n">
         <v>18.1</v>
       </c>
-      <c r="X11" s="15" t="n">
-        <v>20.4</v>
+      <c r="X11" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>99.8</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1427,76 +1464,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>521.2</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E12" s="15" t="n">
+        <v>581.1</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R12" s="14" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="15" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>299.9</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="15" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S12" s="15" t="n">
-        <v>46.9</v>
+      <c r="S12" s="14" t="n">
+        <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>188.6</v>
+        <v>14104.6</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="15" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="14" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>284</v>
+        <v>89</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>23.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1512,25 +1549,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9455.6</v>
+        <v>555.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>11.4</v>
+      <c r="E13" s="14" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1539,49 +1576,47 @@
         <v>8</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="M13" s="15" t="n">
-        <v>717.6</v>
+        <v>11.1</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>19.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>49.3</v>
+        <v>19.2</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>66.8</v>
+      </c>
+      <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>7.8</v>
+      <c r="W13" s="14" t="n">
+        <v>97.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1597,46 +1632,46 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>20319.9</v>
-      </c>
-      <c r="D14" s="15" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>44.1</v>
+      <c r="E14" s="11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>4.5</v>
       </c>
       <c r="H14" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>12.9</v>
-      </c>
       <c r="J14" s="3" t="n">
-        <v>31.6</v>
+        <v>9.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>43.5</v>
+        <v>0.7</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N14" s="15" t="n">
-        <v>820.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>84.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>929</v>
+        <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1647,22 +1682,26 @@
       <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="15" t="n">
-        <v>71.8</v>
+      <c r="T14" s="3" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="W14" s="15" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="W14" s="14" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>25.2</v>
+      </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1680,41 +1719,47 @@
       <c r="C15" s="3" t="n">
         <v>484.5</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="D15" s="11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>12082.1</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="L15" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O15" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P15" s="15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>2.1</v>
+      <c r="P15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q15" s="14" t="n">
+        <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1723,18 +1768,22 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>948</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
+        <v>9648</v>
+      </c>
+      <c r="U15" s="14" t="n">
+        <v>17.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>41.2</v>
+        <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>824.8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>31.6</v>
@@ -1753,47 +1802,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2326.9</v>
-      </c>
-      <c r="D16" s="16" t="n">
+        <v>23069.1</v>
+      </c>
+      <c r="D16" s="11" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>295.7</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>16.2</v>
+      <c r="E16" s="11" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>195481.9</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>139.7</v>
+      </c>
       <c r="J16" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>166.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>19491</v>
+        <v>481.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>115.7</v>
+        <v>1115.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1805,22 +1856,22 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>5.3</v>
+        <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10</v>
+        <v>1100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>190.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99</v>
+        <v>9.9</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1836,72 +1887,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>414.5</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>119.1</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>82.40000000000001</v>
+        <v>4814.1</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>12.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>19.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="15" t="n">
+      <c r="J17" s="14" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="14" t="n">
         <v>13.9</v>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>28.6</v>
+        <v>98.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S17" s="15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="S17" s="14" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>562.6</v>
-      </c>
-      <c r="U17" s="15" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="15" t="n">
-        <v>1.4</v>
+      <c r="V17" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="15" t="n">
-        <v>99.59999999999999</v>
+      <c r="X17" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>898</v>
+        <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>297.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1917,66 +1972,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>335.7</v>
-      </c>
-      <c r="D18" s="9" t="n">
+        <v>955.7</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="11" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="11" t="n">
         <v>19.1</v>
       </c>
-      <c r="G18" s="9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H18" s="15" t="n">
+      <c r="G18" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K18" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="15" t="n">
-        <v>94</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="15" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R18" s="15" t="n">
-        <v>719</v>
+        <v>980.9</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q18" s="14" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="R18" s="14" t="n">
+        <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="15" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W18" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="V18" s="14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W18" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>6.2</v>
+        <v>68</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1992,65 +2057,71 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>19.3</v>
+        <v>455.6</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>19.93</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>14.3</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M19" s="15" t="n">
-        <v>13.8</v>
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>10.8</v>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>196.8</v>
+        <v>41.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.3</v>
+        <v>24.3</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>13.4</v>
+      <c r="S19" s="14" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W19" s="15" t="n">
-        <v>17.5</v>
+        <v>36.1</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V19" s="14" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>98.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>894.8</v>
+        <v>84</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2069,66 +2140,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>494.9</v>
-      </c>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="13" t="n">
-        <v>124.94</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G20" s="15" t="n">
+        <v>1494.9</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>14.3</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>12.4</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>221.4</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="Q20" s="14" t="n">
+        <v>3.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="15" t="n">
+      <c r="S20" s="14" t="n">
         <v>16.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>188</v>
+      </c>
       <c r="U20" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V20" s="14" t="n">
         <v>19.2</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>43.4</v>
+      <c r="W20" s="14" t="n">
+        <v>58.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>21.9</v>
+        <v>8</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2144,28 +2223,28 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>88.8</v>
+        <v>371.3</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>9160.799999999999</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>21.1</v>
@@ -2173,15 +2252,17 @@
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="M21" s="14" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>88.7</v>
+      </c>
       <c r="O21" s="3" t="n">
-        <v>180</v>
+        <v>1808</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
@@ -2190,22 +2271,26 @@
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>80.90000000000001</v>
+      </c>
       <c r="U21" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="V21" s="15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="15" t="n">
-        <v>169.4</v>
+      <c r="W21" s="14" t="n">
+        <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2223,19 +2308,19 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>29.5</v>
+      <c r="D22" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>19.4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H22" s="15" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2245,45 +2330,51 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>21.4</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P22" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="15" t="n">
+      <c r="Q22" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V22" s="15" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>36.1</v>
+        <v>20.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2304,68 +2395,70 @@
         <v>1128.5</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>116.1</v>
+        <v>66.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>110.9</v>
+        <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>115.9</v>
+        <v>15.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>20.5</v>
+        <v>207.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>29489</v>
+        <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1113.6</v>
+        <v>11513.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.5</v>
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2328</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1219.8</v>
+        <v>149.8</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>186.3</v>
+        <v>8.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>938.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9429</v>
+        <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.9</v>
+        <v>1196.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2381,63 +2474,77 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>43791.8</v>
-      </c>
-      <c r="D24" s="16" t="n">
+        <v>4972.9</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="11" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="17" t="inlineStr"/>
-      <c r="G24" s="13" t="n">
-        <v>2156.6</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="F24" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>59.7</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>5.4</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M24" s="15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M24" s="14" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="14" t="n">
+        <v>18</v>
+      </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q24" s="15" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="S24" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="Q24" s="14" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R24" s="14" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="T24" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="15" t="n">
-        <v>189.4</v>
-      </c>
-      <c r="W24" s="3" t="inlineStr"/>
-      <c r="X24" s="15" t="n">
-        <v>8881.200000000001</v>
+      <c r="V24" s="14" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="W24" s="14" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2452,70 +2559,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>13.6</v>
+        <v>253.6</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>2135.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8</v>
+        <v>81.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="L25" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q25" s="15" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="R25" s="15" t="n">
+      <c r="R25" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V25" s="14" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W25" s="14" t="n">
+        <v>22</v>
+      </c>
       <c r="X25" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2531,19 +2644,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>258.3</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F26" s="9" t="n">
+        <v>268.3</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.1</v>
+        <v>17.7</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.5</v>
@@ -2552,51 +2665,55 @@
         <v>0.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="15" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="M26" s="14" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+        <v>88808</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="14" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="15" t="n">
-        <v>15.3</v>
+      <c r="W26" s="14" t="n">
+        <v>15.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>17.2</v>
+        <v>11.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2612,46 +2729,52 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>535.8</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="E27" s="15" t="n">
+        <v>9351.700000000001</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="13" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="F27" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>11.7</v>
+      </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="15" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>28.1</v>
@@ -2662,15 +2785,17 @@
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="15" t="n">
-        <v>19</v>
+      <c r="V27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>88.8</v>
+        <v>28</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>2.8</v>
@@ -2689,61 +2814,67 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>331.3</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>331.8</v>
+      </c>
+      <c r="D28" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="11" t="n">
         <v>9.9</v>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="14" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J28" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K28" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="M28" s="15" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="O28" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="15" t="n">
+      <c r="P28" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>42.2</v>
+      <c r="R28" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>4.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>41.2</v>
+      <c r="W28" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>19.2</v>
@@ -2770,68 +2901,74 @@
       <c r="C29" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E29" s="3" t="n">
+      <c r="D29" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R29" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="15" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N29" s="15" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>991</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R29" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="S29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>856.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="15" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="W29" s="15" t="n">
-        <v>1991</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>17.9</v>
+      <c r="V29" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X29" s="14" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2849,68 +2986,74 @@
       <c r="C30" s="3" t="n">
         <v>1569.9</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="11" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="11" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="16" t="n">
-        <v>194.3</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>154.5</v>
+      <c r="F30" s="11" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>65</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1629.4</v>
+        <v>62.9</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>176.9</v>
+        <v>26.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>8.9</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>444924.4</v>
+        <v>491</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>212.1</v>
+        <v>412.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>998.9</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>9413.799999999999</v>
+        <v>4135.1</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>244.4</v>
+        <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>185.9</v>
+        <v>85.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
+        <v>829.4</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>922</v>
+        <v>6548</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2928,68 +3071,70 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F31" s="9" t="n">
+      <c r="D31" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" s="16" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="H31" s="3" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H31" s="14" t="n">
         <v>12.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L31" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
+      <c r="M31" s="14" t="n">
+        <v>19.9</v>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>1454.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
+      <c r="R31" s="14" t="n">
+        <v>7.8</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>8115.4</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="W31" s="15" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>18.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="V31" s="14" t="n">
+        <v>8010.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3007,59 +3152,73 @@
       <c r="C32" s="3" t="n">
         <v>364.2</v>
       </c>
-      <c r="D32" s="13" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>282.13</v>
+      <c r="D32" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="15" t="n">
-        <v>19.6</v>
+        <v>79.3</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="R32" s="15" t="n">
+      <c r="R32" s="14" t="n">
         <v>14.8</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V32" s="3" t="inlineStr"/>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="V32" s="14" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W32" s="14" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X32" s="14" t="n">
+        <v>181.7</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3076,68 +3235,74 @@
       <c r="C33" s="3" t="n">
         <v>411.2</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="3" t="n">
+      <c r="D33" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="H33" s="14" t="n">
         <v>11.5</v>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>0.8</v>
+        <v>11.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M33" s="15" t="n">
-        <v>1097.2</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>62.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="15" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="15" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="V33" s="3" t="n">
+      <c r="Q33" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R33" s="14" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V33" s="14" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X33" s="15" t="n">
-        <v>980</v>
+      <c r="W33" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X33" s="14" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3153,68 +3318,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1144.4</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="9" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E34" s="11" t="n">
         <v>15.1</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>17.4</v>
+      <c r="F34" s="11" t="n">
+        <v>17.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+        <v>9.6</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2.5</v>
+        <v>98.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="N34" s="3" t="n">
-        <v>18.8</v>
+        <v>91.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q34" s="14" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" s="15" t="n">
-        <v>16.9</v>
-      </c>
       <c r="W34" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="X34" s="15" t="n">
-        <v>16.6</v>
+        <v>15.2</v>
+      </c>
+      <c r="X34" s="14" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>90.8</v>
+        <v>20</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3232,26 +3405,26 @@
       <c r="C35" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G35" s="9" t="n">
+      <c r="F35" s="11" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="G35" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>9.9</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0.1</v>
@@ -3259,11 +3432,11 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="15" t="n">
-        <v>21281.8</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>19.9</v>
+      <c r="M35" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>14.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>98</v>
@@ -3272,32 +3445,34 @@
         <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>23.9</v>
+        <v>29.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="T35" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>68.8</v>
+      </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>48.4</v>
+        <v>18.9</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>17.7</v>
+        <v>18.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3316,69 +3491,73 @@
         <v>613.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>10.9</v>
+        <v>25.7</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>105.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.3</v>
+        <v>93.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="15" t="n">
-        <v>115</v>
+      <c r="L36" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>16.4</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q36" s="15" t="n">
-        <v>27</v>
+        <v>18.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" s="15" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V36" s="15" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V36" s="14" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="X36" s="15" t="n">
-        <v>32.6</v>
+        <v>17.2</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>10.8</v>
+        <v>28.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3394,76 +3573,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>19782.4</v>
+        <v>2078.2</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>1118.4</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>1092.2</v>
+        <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.9</v>
+        <v>56.1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>819.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>150.1</v>
+        <v>5071.7</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1681.5</v>
+        <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>167.6</v>
+        <v>62.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>9492</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>401.2</v>
+        <v>101</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>382191.4</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>233.2</v>
+        <v>93.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.9</v>
+        <v>90</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>181.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>42.9</v>
+        <v>429.9</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3481,66 +3660,74 @@
       <c r="C38" s="3" t="n">
         <v>495.6</v>
       </c>
-      <c r="D38" s="17" t="inlineStr"/>
-      <c r="E38" s="13" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="F38" s="16" t="n">
+      <c r="D38" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F38" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J38" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="n">
+      <c r="G38" s="14" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M38" s="14" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.9</v>
+        <v>41.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S38" s="15" t="n">
-        <v>172</v>
+        <v>20.2</v>
+      </c>
+      <c r="R38" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="S38" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
-      <c r="U38" s="15" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="V38" s="15" t="n">
-        <v>8101.4</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V38" s="14" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>16.3</v>
+      </c>
       <c r="X38" s="3" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>184.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>9.1</v>
+        <v>81.2</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3556,68 +3743,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F39" s="9" t="n">
+        <v>664.1</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J39" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="15" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="15" t="n">
-        <v>2120.2</v>
+        <v>8.1</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P39" s="15" t="n">
+      <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="15" t="n">
-        <v>24.8</v>
+      <c r="Q39" s="14" t="n">
+        <v>69.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S39" s="15" t="n">
-        <v>50.5</v>
+        <v>8.9</v>
+      </c>
+      <c r="S39" s="14" t="n">
+        <v>521</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="U39" s="14" t="n">
         <v>12.8</v>
       </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="15" t="n">
-        <v>98.8</v>
+      <c r="V39" s="14" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W39" s="14" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>162.8</v>
+        <v>64</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3635,17 +3830,17 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="D40" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="9" t="n">
-        <v>16.3</v>
+      <c r="G40" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="n">
@@ -3655,52 +3850,52 @@
         <v>5.7</v>
       </c>
       <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="14" t="n">
         <v>10</v>
-      </c>
-      <c r="L40" s="15" t="n">
-        <v>110</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="N40" s="15" t="n">
-        <v>21.9</v>
+      <c r="N40" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Q40" s="15" t="n">
-        <v>35.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0.2</v>
+        <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="V40" s="15" t="n">
-        <v>22.3</v>
+      <c r="V40" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X40" s="15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>59</v>
+        <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3716,68 +3911,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>794.3</v>
-      </c>
-      <c r="D41" s="9" t="n">
+        <v>694.3</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="J41" s="3" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="15" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R41" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="M41" s="14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="14" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="S41" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>17.9</v>
+        <v>12</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="W41" s="15" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="15" t="n">
-        <v>22.8</v>
+      <c r="X41" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3793,72 +3996,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>608.8</v>
-      </c>
-      <c r="D42" s="9" t="n">
+        <v>208.8</v>
+      </c>
+      <c r="D42" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>16.1</v>
+      <c r="E42" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15.8</v>
+        <v>53.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>35.9</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
+      <c r="L42" s="14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N42" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="O42" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>949</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>49</v>
+      </c>
+      <c r="U42" s="14" t="n">
+        <v>47.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="15" t="n">
+      <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.2</v>
+        <v>28.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3874,41 +4081,47 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>604.4</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="D43" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="14" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>81</v>
+      <c r="G43" s="9" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K43" s="15" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="3" t="n">
-        <v>434</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
+      <c r="L43" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>1021.9</v>
+      </c>
+      <c r="N43" s="14" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
       </c>
@@ -3919,25 +4132,25 @@
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>2.8</v>
       </c>
       <c r="U43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W43" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="Y43" s="3" t="n">
         <v>39.9</v>
       </c>
-      <c r="V43" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>729.8</v>
-      </c>
       <c r="Z43" s="3" t="n">
-        <v>20.3</v>
+        <v>211.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3952,10 +4165,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3993,13 +4208,13 @@
         <v>3119.5</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>431.1</v>
+        <v>131.9</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>3.6</v>
+        <v>23.6</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
@@ -4008,58 +4223,58 @@
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1181.9</v>
+        <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>356.4</v>
+        <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>168.9</v>
+        <v>61.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>124.8</v>
+        <v>121</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1126.3</v>
+        <v>126.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>29.2</v>
+        <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1282.2</v>
+        <v>212.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1108.9</v>
+        <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1060.9</v>
+        <v>658</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>23028.1</v>
+        <v>382.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.5</v>
+        <v>281.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4077,63 +4292,73 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="13" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>50.3</v>
+      <c r="E46" s="9" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J46" s="15" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="15" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="M46" s="15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q46" s="15" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="R46" s="15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>1219.8</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>900.1</v>
+      </c>
+      <c r="P46" s="14" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="R46" s="14" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="15" t="n">
+      <c r="S46" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="U46" s="14" t="n">
         <v>865.4</v>
       </c>
-      <c r="V46" s="15" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W46" s="15" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="V46" s="14" t="n">
+        <v>1541.6</v>
+      </c>
+      <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>181.4</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -55,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,19 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,10 +167,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,23 +786,23 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F4" s="11" t="n">
+      <c r="E4" s="10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="10" t="n">
         <v>12.1</v>
       </c>
       <c r="H4" s="14" t="n">
         <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -814,28 +814,28 @@
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>15.7</v>
+        <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P4" s="14" t="n">
-        <v>20.2</v>
+        <v>99</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="Q4" s="14" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="14" t="n">
-        <v>89.3</v>
+      <c r="R4" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
@@ -843,8 +843,8 @@
       <c r="V4" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="14" t="n">
-        <v>12</v>
+      <c r="W4" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
@@ -853,7 +853,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -869,16 +869,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>20.5</v>
+        <v>14649.5</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>12.5</v>
@@ -893,7 +893,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>14</v>
@@ -905,7 +905,7 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>95.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.4</v>
@@ -926,9 +926,9 @@
         <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W5" s="14" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="W5" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -938,7 +938,7 @@
         <v>93</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -956,20 +956,20 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="D6" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>19.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>110.6</v>
+      <c r="H6" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>11.2</v>
@@ -978,23 +978,21 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.6</v>
+        <v>14.2</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>21562.1</v>
+        <v>256.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -1017,13 +1015,13 @@
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1039,18 +1037,18 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F7" s="11" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="10" t="n">
         <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1066,7 +1064,7 @@
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>15.2</v>
@@ -1075,7 +1073,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>8.4</v>
@@ -1087,13 +1085,13 @@
         <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>7.7</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
@@ -1124,15 +1122,15 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F8" s="11" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1144,26 +1142,26 @@
       <c r="I8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="14" t="n">
-        <v>14.1</v>
+      <c r="J8" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="M8" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="N8" s="14" t="n">
-        <v>31.4</v>
+        <v>13.1</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
+        <v>4.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
@@ -1180,11 +1178,11 @@
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="14" t="n">
-        <v>29.8</v>
+      <c r="V8" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>97.8</v>
+        <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>19.2</v>
@@ -1211,17 +1209,17 @@
       <c r="C9" s="3" t="n">
         <v>1825.2</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>126.5</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>71.5</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>5</v>
+      <c r="G9" s="10" t="n">
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>61.5</v>
@@ -1229,38 +1227,36 @@
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>1281.9</v>
+        <v>28.9</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>423.8</v>
+        <v>422</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>10.3</v>
+        <v>103.3</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>985.6</v>
+        <v>9285.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>910.1</v>
+        <v>891.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1272,13 +1268,13 @@
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>949.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94290.8</v>
+        <v>9429.799999999999</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16.7</v>
+        <v>116.9</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1296,44 +1292,44 @@
       <c r="C10" s="3" t="n">
         <v>3650.1</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <v>11</v>
+      <c r="G10" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>41.2</v>
+        <v>12.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L10" s="14" t="n">
-        <v>58</v>
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>83.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>2</v>
@@ -1345,15 +1341,15 @@
         <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W10" s="14" t="n">
+      <c r="W10" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1382,13 +1378,13 @@
         <v>329.6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>13.9</v>
+        <v>23.9</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1403,49 +1399,49 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L11" s="14" t="n">
-        <v>12.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>52.7</v>
+        <v>5.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.6</v>
+        <v>231.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>80.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="14" t="n">
-        <v>62.3</v>
+        <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>21.9</v>
+      <c r="S11" s="14" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="V11" s="14" t="n">
-        <v>15</v>
+        <v>188.6</v>
       </c>
       <c r="W11" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>28.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="X11" s="14" t="n">
+        <v>18.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>99.8</v>
+        <v>98.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1</v>
@@ -1464,58 +1460,56 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>581.1</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F12" s="14" t="n">
+        <v>501.1</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>1.8</v>
+      <c r="G12" s="10" t="n">
+        <v>11.8</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J12" s="14" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>14.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.8</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="R12" s="14" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="S12" s="14" t="n">
+      <c r="R12" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>14104.6</v>
+        <v>18.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1533,7 +1527,7 @@
         <v>89</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1549,19 +1543,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>555.6</v>
+        <v>155.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>37.1</v>
+      <c r="E13" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1575,20 +1569,20 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>11.1</v>
+      <c r="L13" s="14" t="n">
+        <v>11.2</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>19.6</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1596,18 +1590,20 @@
       <c r="R13" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>19.7</v>
+      <c r="S13" s="14" t="n">
+        <v>29.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="U13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="14" t="n">
-        <v>97.8</v>
+      <c r="W13" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
@@ -1616,7 +1612,7 @@
         <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1632,19 +1628,19 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>4.5</v>
+      <c r="G14" s="10" t="n">
+        <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>8.9</v>
@@ -1653,10 +1649,10 @@
         <v>2.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="L14" s="14" t="n">
         <v>12.5</v>
@@ -1664,8 +1660,8 @@
       <c r="M14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>84.3</v>
+      <c r="N14" s="14" t="n">
+        <v>94.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
@@ -1683,19 +1679,19 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>171.1</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>17.8</v>
+        <v>7.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="14" t="n">
-        <v>18.4</v>
+      <c r="W14" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>25.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
@@ -1717,25 +1713,25 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>484.5</v>
-      </c>
-      <c r="D15" s="11" t="n">
+        <v>454.5</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="10" t="n">
         <v>14.1</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="10" t="n">
         <v>13.6</v>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>12082.1</v>
+      <c r="H15" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.4</v>
+        <v>0.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1744,13 +1740,13 @@
         <v>11.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.7</v>
+        <v>18.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>97</v>
@@ -1758,7 +1754,7 @@
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="14" t="n">
+      <c r="Q15" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1768,22 +1764,22 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>9648</v>
-      </c>
-      <c r="U15" s="14" t="n">
+        <v>248</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.6</v>
+        <v>1.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>824.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>31.6</v>
@@ -1802,49 +1798,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>23069.1</v>
-      </c>
-      <c r="D16" s="11" t="n">
+        <v>2306.9</v>
+      </c>
+      <c r="D16" s="15" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="F16" s="11" t="n">
+      <c r="E16" s="15" t="n">
+        <v>655.3</v>
+      </c>
+      <c r="F16" s="15" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>58.9</v>
+        <v>48.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>139.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
+        <v>134.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>481.8</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1115.7</v>
+        <v>118.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1859,16 +1855,16 @@
         <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1100.4</v>
+        <v>100.9</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>9421</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>118.4</v>
@@ -1887,19 +1883,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4814.1</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E17" s="11" t="n">
+        <v>814.1</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>12.9</v>
+      <c r="F17" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1907,23 +1903,23 @@
       <c r="I17" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J17" s="14" t="n">
-        <v>16.4</v>
+      <c r="J17" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.6</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98.8</v>
+        <v>28.6</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1934,7 +1930,7 @@
       <c r="R17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="S17" s="14" t="n">
+      <c r="S17" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1956,7 +1952,7 @@
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1974,47 +1970,45 @@
       <c r="C18" s="3" t="n">
         <v>955.7</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="10" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="H18" s="3" t="n">
+      <c r="G18" s="10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H18" s="14" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.5</v>
+        <v>25.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>182.2</v>
+        <v>18</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>980.9</v>
+        <v>982.8</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q18" s="14" t="n">
-        <v>66.40000000000001</v>
+        <v>216.8</v>
       </c>
       <c r="R18" s="14" t="n">
         <v>19</v>
@@ -2023,25 +2017,25 @@
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V18" s="14" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>68</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2057,16 +2051,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>19.93</v>
+      <c r="E19" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>1.2</v>
@@ -2078,47 +2072,49 @@
         <v>5.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>14.3</v>
+        <v>1.3</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L19" s="14" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="M19" s="14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>15.5</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>41.8</v>
+        <v>92.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="14" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="U19" s="14" t="n">
-        <v>29.4</v>
+        <v>23.4</v>
       </c>
       <c r="V19" s="14" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="W19" s="14" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>28.9</v>
+        <v>19.9</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>84</v>
@@ -2140,36 +2136,36 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1494.9</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="G20" s="11" t="n">
+        <v>1497.9</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>14.3</v>
+        <v>2.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="M20" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2177,34 +2173,34 @@
         <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="14" t="n">
-        <v>3.5</v>
+        <v>23.9</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="14" t="n">
+      <c r="S20" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V20" s="14" t="n">
-        <v>19.2</v>
+        <v>91.2</v>
       </c>
       <c r="W20" s="14" t="n">
-        <v>58.8</v>
+        <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>8</v>
@@ -2225,23 +2221,23 @@
       <c r="C21" s="3" t="n">
         <v>371.3</v>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>9160.799999999999</v>
-      </c>
-      <c r="F21" s="11" t="n">
+      <c r="D21" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F21" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>89.5</v>
+        <v>15.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>2.7</v>
@@ -2259,7 +2255,7 @@
         <v>88.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1808</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>8</v>
@@ -2271,25 +2267,25 @@
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="14" t="n">
+      <c r="W21" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2308,17 +2304,17 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>19.4</v>
+      <c r="D22" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>29.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>10.6</v>
@@ -2326,39 +2322,41 @@
       <c r="I22" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N22" s="14" t="n">
-        <v>21.4</v>
+        <v>1.3</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q22" s="14" t="n">
-        <v>4.6</v>
+        <v>224.6</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>18.7</v>
+        <v>185.4</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>1.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
@@ -2367,7 +2365,7 @@
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20.1</v>
+        <v>28.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
@@ -2391,17 +2389,17 @@
       <c r="C23" s="3" t="n">
         <v>2089.4</v>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>1128.5</v>
-      </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="15" t="n">
+        <v>1128.4</v>
+      </c>
+      <c r="E23" s="15" t="n">
         <v>66.8</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="15" t="n">
         <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
@@ -2416,49 +2414,45 @@
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>207.1</v>
+        <v>20.7</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>6.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>71.8</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>11513.6</v>
+        <v>115.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>91.8</v>
-      </c>
+        <v>918.5</v>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>328</v>
+        <v>3260.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
+        <v>49.8</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>8.6</v>
+        <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>938.9</v>
+        <v>93.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1196.3</v>
+        <v>198.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2474,58 +2468,56 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4972.9</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>4912.9</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>23.4</v>
       </c>
-      <c r="H24" s="14" t="n">
-        <v>8.5</v>
+      <c r="H24" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>5.4</v>
-      </c>
+        <v>37.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>14.7</v>
+        <v>1.4</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="14" t="n">
-        <v>18</v>
+      <c r="N24" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P24" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q24" s="14" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R24" s="14" t="n">
-        <v>85.3</v>
+      <c r="P24" s="14" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>6.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
@@ -2533,8 +2525,8 @@
       <c r="V24" s="14" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="W24" s="14" t="n">
-        <v>73.09999999999999</v>
+      <c r="W24" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>18.7</v>
@@ -2543,7 +2535,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2559,49 +2551,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>253.6</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="F25" s="11" t="n">
+        <v>223.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>2135.6</v>
+        <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>81.7</v>
+        <v>8.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="L25" s="14" t="n">
-        <v>96.2</v>
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="N25" s="14" t="n">
-        <v>12.1</v>
+      <c r="N25" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2610,25 +2602,25 @@
         <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="V25" s="14" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="W25" s="14" t="n">
-        <v>22</v>
+      <c r="W25" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>93.8</v>
+        <v>920.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2646,27 +2638,25 @@
       <c r="C26" s="3" t="n">
         <v>268.3</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
@@ -2674,18 +2664,18 @@
         <v>15.8</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>88808</v>
+        <v>908.8</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q26" s="14" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2695,7 +2685,7 @@
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2704,13 +2694,13 @@
         <v>15.6</v>
       </c>
       <c r="W26" s="14" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>11.2</v>
+        <v>15.3</v>
+      </c>
+      <c r="X26" s="14" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0.6</v>
@@ -2729,25 +2719,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9351.700000000001</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>435.8</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="9" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="H27" s="14" t="n">
+      <c r="G27" s="16" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="I27" s="14" t="n">
-        <v>11.7</v>
+      <c r="I27" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2756,21 +2746,21 @@
         <v>13.2</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M27" s="14" t="n">
-        <v>25.8</v>
+        <v>13.5</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q27" s="14" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2779,14 +2769,12 @@
       <c r="S27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>87</v>
-      </c>
+      <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
@@ -2795,7 +2783,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>2.8</v>
@@ -2814,25 +2802,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>331.8</v>
-      </c>
-      <c r="D28" s="11" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="D28" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="10" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="10" t="n">
         <v>9.9</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I28" s="14" t="n">
-        <v>7.5</v>
+      <c r="I28" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.3</v>
@@ -2844,7 +2832,7 @@
         <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>16.2</v>
@@ -2865,10 +2853,10 @@
         <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2901,18 +2889,16 @@
       <c r="C29" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="D29" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
@@ -2926,7 +2912,7 @@
         <v>0.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>15</v>
@@ -2941,7 +2927,7 @@
         <v>10.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R29" s="14" t="n">
         <v>19</v>
@@ -2959,16 +2945,16 @@
         <v>13.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X29" s="14" t="n">
-        <v>79.40000000000001</v>
+        <v>1.5</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2986,17 +2972,17 @@
       <c r="C30" s="3" t="n">
         <v>1569.9</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="10" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="10" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="10" t="n">
         <v>94.3</v>
       </c>
-      <c r="G30" s="9" t="n">
-        <v>65</v>
+      <c r="G30" s="16" t="n">
+        <v>64.59999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>62.9</v>
@@ -3005,55 +2991,53 @@
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.9</v>
+        <v>69</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>491</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>412.1</v>
-      </c>
+        <v>491.8</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="n">
-        <v>998.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4135.1</v>
+        <v>413.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.7</v>
+        <v>8.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>829.4</v>
+        <v>824.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6548</v>
+        <v>94228</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3071,29 +3055,29 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="16" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F31" s="16" t="n">
+      <c r="D31" s="10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="H31" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>8.1</v>
+      <c r="I31" s="14" t="n">
+        <v>81.5</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="L31" s="14" t="n">
         <v>15</v>
@@ -3103,38 +3087,36 @@
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>1454.4</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1644.1</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="14" t="n">
-        <v>7.8</v>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>9211.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="14" t="n">
-        <v>8010.1</v>
+        <v>8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3153,39 +3135,41 @@
         <v>364.2</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="F32" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F32" s="16" t="n">
         <v>31</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>79.3</v>
+        <v>29.1</v>
       </c>
       <c r="L32" s="14" t="n">
         <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -3193,31 +3177,31 @@
         <v>13</v>
       </c>
       <c r="R32" s="14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
         <v>14.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>1.8</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>8</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="V32" s="14" t="n">
-        <v>26.6</v>
+        <v>16.6</v>
       </c>
       <c r="W32" s="14" t="n">
         <v>16.2</v>
       </c>
-      <c r="X32" s="14" t="n">
-        <v>181.7</v>
+      <c r="X32" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3235,17 +3219,17 @@
       <c r="C33" s="3" t="n">
         <v>411.2</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="10" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>100.8</v>
+      <c r="E33" s="10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="H33" s="14" t="n">
         <v>11.5</v>
@@ -3259,14 +3243,14 @@
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="14" t="n">
-        <v>4.9</v>
+      <c r="L33" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12.7</v>
+        <v>11.7</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>62.8</v>
+        <v>60.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3275,34 +3259,34 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R33" s="14" t="n">
-        <v>86.40000000000001</v>
+        <v>21.2</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V33" s="14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W33" s="14" t="n">
         <v>16.5</v>
       </c>
-      <c r="X33" s="14" t="n">
-        <v>87.09999999999999</v>
+      <c r="X33" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3320,17 +3304,17 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>17.8</v>
+      <c r="D34" s="14" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="14" t="n">
         <v>14.2</v>
@@ -3339,28 +3323,26 @@
         <v>0.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>98.5</v>
+        <v>3.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>15.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>91.8</v>
+        <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="14" t="n">
-        <v>96.90000000000001</v>
+      <c r="Q34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>15.8</v>
@@ -3369,22 +3351,22 @@
         <v>1.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="X34" s="14" t="n">
-        <v>86.59999999999999</v>
+      <c r="X34" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>8</v>
@@ -3403,18 +3385,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>477.8</v>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F35" s="11" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="G35" s="11" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G35" s="10" t="n">
         <v>12.1</v>
       </c>
       <c r="H35" s="14" t="n">
@@ -3424,7 +3406,7 @@
         <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0.1</v>
@@ -3435,23 +3417,21 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="14" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>29.9</v>
+        <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
+      </c>
+      <c r="S35" s="14" t="n">
+        <v>15.9</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>68.8</v>
@@ -3459,14 +3439,14 @@
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="14" t="n">
         <v>18.9</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>81</v>
@@ -3490,23 +3470,23 @@
       <c r="C36" s="3" t="n">
         <v>613.2</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>71.38</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="D36" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G36" s="10" t="n">
         <v>11.5</v>
       </c>
       <c r="H36" s="14" t="n">
-        <v>105.9</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>93.5</v>
+        <v>3.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4.8</v>
@@ -3515,22 +3495,22 @@
         <v>0</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>16.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>870.8</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>18.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3539,22 +3519,22 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>31.1</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V36" s="14" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1</v>
@@ -3575,13 +3555,13 @@
       <c r="C37" s="3" t="n">
         <v>2078.2</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="15" t="n">
         <v>1118.4</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="15" t="n">
         <v>6.6</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="15" t="n">
         <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3591,28 +3571,28 @@
         <v>56.1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>819.4</v>
+        <v>181.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>5071.7</v>
+        <v>50.7</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>62.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
@@ -3621,13 +3601,13 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3801.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>93.2</v>
+        <v>33.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>90</v>
@@ -3639,10 +3619,10 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.9</v>
+        <v>422.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3658,31 +3638,31 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>495.6</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E38" s="11" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E38" s="15" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="15" t="n">
         <v>18.4</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>25.1</v>
+        <v>35.1</v>
       </c>
       <c r="H38" s="14" t="n">
-        <v>61.5</v>
+        <v>66.5</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>17</v>
+        <v>170.2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="L38" s="14" t="n">
         <v>13.7</v>
@@ -3694,28 +3674,28 @@
         <v>41.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="14" t="n">
-        <v>117</v>
+      <c r="R38" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="14" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>2.6</v>
+        <v>16.1</v>
       </c>
       <c r="V38" s="14" t="n">
-        <v>80.09999999999999</v>
+        <v>18</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>16.3</v>
@@ -3724,10 +3704,10 @@
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.2</v>
+        <v>9.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3743,18 +3723,18 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>664.1</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E39" s="11" t="n">
+        <v>624.4</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>11.1</v>
       </c>
-      <c r="F39" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="F39" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G39" s="10" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3767,49 +3747,49 @@
         <v>5.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="14" t="n">
-        <v>69.8</v>
+      <c r="Q39" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="S39" s="14" t="n">
-        <v>521</v>
+      <c r="S39" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="U39" s="14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V39" s="14" t="n">
-        <v>27.5</v>
+        <v>26</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="14" t="n">
         <v>62.5</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3830,19 +3810,21 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
@@ -3852,11 +3834,11 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="L40" s="3" t="n">
         <v>10</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12</v>
@@ -3865,16 +3847,16 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>48.9</v>
@@ -3883,7 +3865,7 @@
         <v>16.7</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>20.3</v>
+        <v>25.3</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>17.3</v>
@@ -3895,7 +3877,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3911,40 +3893,38 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>694.3</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>699.3</v>
+      </c>
+      <c r="D41" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G41" s="11" t="n">
+      <c r="E41" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>110.7</v>
-      </c>
-      <c r="M41" s="14" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>98</v>
@@ -3952,35 +3932,35 @@
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="14" t="n">
-        <v>293.5</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>18.2</v>
+      <c r="Q41" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="R41" s="14" t="n">
+        <v>72.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>58.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V41" s="14" t="n">
+        <v>641.7</v>
+      </c>
+      <c r="W41" s="14" t="n">
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28.8</v>
+        <v>1.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3996,49 +3976,49 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>208.8</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>608.8</v>
+      </c>
+      <c r="D42" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>53.8</v>
+        <v>3.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="14" t="n">
-        <v>11.9</v>
+      <c r="L42" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>18.1</v>
+        <v>13.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>26.7</v>
+      <c r="Q42" s="14" t="n">
+        <v>61.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
@@ -4049,8 +4029,8 @@
       <c r="T42" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="U42" s="14" t="n">
-        <v>47.4</v>
+      <c r="U42" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
@@ -4059,13 +4039,13 @@
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4081,19 +4061,19 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>5049.4</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>26.1</v>
       </c>
       <c r="E43" s="14" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="G43" s="9" t="n">
-        <v>162.8</v>
+      <c r="G43" s="16" t="n">
+        <v>12.8</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>8</v>
@@ -4111,16 +4091,16 @@
         <v>13</v>
       </c>
       <c r="M43" s="14" t="n">
-        <v>1021.9</v>
-      </c>
-      <c r="N43" s="14" t="n">
-        <v>52.1</v>
+        <v>122.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>97</v>
+        <v>972</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
@@ -4132,25 +4112,25 @@
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W43" s="14" t="n">
-        <v>68</v>
+      <c r="W43" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>211.9</v>
+        <v>210.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4168,7 +4148,7 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
+      <c r="D44" s="10" t="inlineStr"/>
       <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
@@ -4207,14 +4187,14 @@
       <c r="C45" s="3" t="n">
         <v>3119.5</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="15" t="n">
         <v>131.9</v>
       </c>
-      <c r="E45" s="16" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>92.3</v>
+      <c r="E45" s="15" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
@@ -4226,13 +4206,13 @@
         <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27.2</v>
+        <v>127.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
+        <v>36.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>55.9</v>
@@ -4241,10 +4221,10 @@
         <v>61.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>490</v>
+        <v>298</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>126.3</v>
@@ -4253,28 +4233,28 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>212.5</v>
+        <v>2172.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>7.6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>658</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>382.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>281.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4292,20 +4272,20 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="16" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G46" s="16" t="n">
         <v>101.5</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="G46" s="9" t="n">
-        <v>20</v>
-      </c>
       <c r="H46" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>3.8</v>
@@ -4313,20 +4293,20 @@
       <c r="J46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" s="14" t="n">
-        <v>1111</v>
+      <c r="K46" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="L46" s="14" t="n">
-        <v>1219.8</v>
+        <v>1213.8</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>111.9</v>
+        <v>101.9</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>35.1</v>
+        <v>32.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>900.1</v>
+        <v>9</v>
       </c>
       <c r="P46" s="14" t="n">
         <v>24.1</v>
@@ -4335,7 +4315,7 @@
         <v>25.3</v>
       </c>
       <c r="R46" s="14" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>1.6</v>
@@ -4344,20 +4324,20 @@
         <v>59.8</v>
       </c>
       <c r="U46" s="14" t="n">
-        <v>865.4</v>
+        <v>365.4</v>
       </c>
       <c r="V46" s="14" t="n">
-        <v>1541.6</v>
+        <v>1841.6</v>
       </c>
       <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>69.2</v>
+        <v>21.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>181.4</v>
+        <v>18.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,22 +161,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -813,7 +816,7 @@
       <c r="L4" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -828,7 +831,7 @@
       <c r="Q4" s="14" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="10" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -840,10 +843,10 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -913,7 +916,7 @@
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -925,10 +928,10 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -980,7 +983,7 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="11" t="n">
         <v>1.3</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -996,7 +999,7 @@
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1008,10 +1011,10 @@
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1081,7 +1084,7 @@
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1093,10 +1096,10 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1166,7 +1169,7 @@
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1178,10 +1181,10 @@
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1228,13 +1231,13 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="15" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="15" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1246,10 +1249,10 @@
       <c r="P9" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="15" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="10" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1261,10 +1264,10 @@
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>95.5</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="15" t="n">
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1316,10 +1319,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="15" t="n">
         <v>15.8</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="15" t="n">
         <v>19.2</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1331,10 +1334,10 @@
       <c r="P10" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="10" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1346,10 +1349,10 @@
       <c r="U10" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>19.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1416,7 +1419,7 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="11" t="n">
         <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1431,8 +1434,8 @@
       <c r="U11" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="V11" s="14" t="n">
-        <v>188.6</v>
+      <c r="V11" s="10" t="n">
+        <v>18.86</v>
       </c>
       <c r="W11" s="14" t="n">
         <v>18.9</v>
@@ -1502,7 +1505,7 @@
       <c r="Q12" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="11" t="n">
         <v>2.5</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1514,7 +1517,7 @@
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="14" t="n">
@@ -1599,7 +1602,7 @@
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1684,7 +1687,7 @@
       <c r="U14" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1769,7 +1772,7 @@
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="10" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1821,13 +1824,13 @@
       <c r="J16" s="3" t="n">
         <v>134.9</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="15" t="n">
         <v>19.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="15" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="15" t="n">
         <v>6.8</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1839,10 +1842,10 @@
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="15" t="n">
         <v>118.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="15" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1854,10 +1857,10 @@
       <c r="U16" s="3" t="n">
         <v>55.8</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="15" t="n">
         <v>100.9</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="15" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1909,10 +1912,10 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="14" t="n">
+      <c r="L17" s="15" t="n">
         <v>13.4</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="15" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1924,10 +1927,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="15" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="15" t="n">
         <v>11.8</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1939,10 +1942,10 @@
       <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="15" t="n">
         <v>18.2</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -2007,10 +2010,10 @@
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="14" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="R18" s="14" t="n">
+      <c r="Q18" s="11" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="R18" s="10" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2025,7 +2028,7 @@
       <c r="V18" s="14" t="n">
         <v>10.2</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2056,7 +2059,7 @@
       <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="11" t="n">
         <v>63</v>
       </c>
       <c r="F19" s="14" t="n">
@@ -2095,7 +2098,7 @@
       <c r="Q19" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="10" t="n">
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2110,7 +2113,7 @@
       <c r="V19" s="14" t="n">
         <v>19.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="14" t="n">
@@ -2178,7 +2181,7 @@
       <c r="Q20" s="14" t="n">
         <v>23.9</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2190,10 +2193,10 @@
       <c r="U20" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V20" s="14" t="n">
+      <c r="V20" s="11" t="n">
         <v>91.2</v>
       </c>
-      <c r="W20" s="14" t="n">
+      <c r="W20" s="10" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2263,7 +2266,7 @@
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="10" t="n">
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2278,7 +2281,7 @@
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="10" t="n">
         <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2328,11 +2331,11 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" s="14" t="n">
-        <v>120.9</v>
+      <c r="M22" s="11" t="n">
+        <v>12.09</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>1.4</v>
@@ -2343,11 +2346,11 @@
       <c r="P22" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q22" s="14" t="n">
-        <v>224.6</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>185.4</v>
+      <c r="Q22" s="11" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>18.54</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>1.8</v>
@@ -2361,7 +2364,7 @@
       <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="10" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2410,13 +2413,13 @@
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="15" t="n">
         <v>27.9</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="15" t="n">
         <v>20.7</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="15" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2426,10 +2429,10 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="15" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="15" t="n">
         <v>918.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -2439,10 +2442,10 @@
       <c r="U23" s="3" t="n">
         <v>49.8</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="15" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="15" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2492,10 +2495,10 @@
         <v>37.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="15" t="n">
         <v>1.4</v>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="M24" s="15" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2507,10 +2510,10 @@
       <c r="P24" s="14" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="15" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2522,10 +2525,10 @@
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="14" t="n">
+      <c r="V24" s="15" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="10" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2592,7 +2595,7 @@
       <c r="P25" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
@@ -2607,10 +2610,10 @@
       <c r="U25" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="V25" s="14" t="n">
+      <c r="V25" s="11" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="11" t="n">
         <v>0.1</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2675,7 +2678,7 @@
       <c r="P26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2730,7 +2733,7 @@
       <c r="F27" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="11" t="n">
         <v>13.1</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2748,7 +2751,7 @@
       <c r="L27" s="14" t="n">
         <v>13.5</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="11" t="n">
         <v>1.9</v>
       </c>
       <c r="N27" s="14" t="n">
@@ -2760,7 +2763,7 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="14" t="n">
+      <c r="Q27" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2843,7 +2846,7 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
         <v>19.6</v>
       </c>
       <c r="R28" s="14" t="n">
@@ -2911,7 +2914,7 @@
       <c r="K29" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="11" t="n">
         <v>3.7</v>
       </c>
       <c r="M29" s="14" t="n">
@@ -2926,7 +2929,7 @@
       <c r="P29" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="R29" s="14" t="n">
@@ -2944,7 +2947,7 @@
       <c r="V29" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2981,7 +2984,7 @@
       <c r="F30" s="10" t="n">
         <v>94.3</v>
       </c>
-      <c r="G30" s="16" t="n">
+      <c r="G30" s="11" t="n">
         <v>64.59999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -2993,13 +2996,13 @@
       <c r="J30" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="15" t="n">
         <v>26.9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="15" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="15" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3009,10 +3012,10 @@
         <v>491.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="15" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="15" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3024,10 +3027,10 @@
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="15" t="n">
         <v>8.5</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="15" t="n">
         <v>824.9</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3079,10 +3082,10 @@
       <c r="K31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L31" s="14" t="n">
+      <c r="L31" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="14" t="n">
+      <c r="M31" s="15" t="n">
         <v>19.9</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
@@ -3090,10 +3093,10 @@
         <v>1644.1</v>
       </c>
       <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="15" t="n">
         <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3105,10 +3108,10 @@
       <c r="U31" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V31" s="14" t="n">
+      <c r="V31" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="15" t="n">
         <v>16.3</v>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
@@ -3140,7 +3143,7 @@
       <c r="E32" s="14" t="n">
         <v>11.9</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="11" t="n">
         <v>31</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3173,10 +3176,10 @@
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="R32" s="14" t="n">
+      <c r="R32" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3188,10 +3191,10 @@
       <c r="U32" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="V32" s="14" t="n">
+      <c r="V32" s="10" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="14" t="n">
+      <c r="W32" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3243,7 +3246,7 @@
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3258,10 +3261,10 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3273,10 +3276,10 @@
       <c r="U33" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="10" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="14" t="n">
+      <c r="W33" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3307,7 +3310,7 @@
       <c r="D34" s="14" t="n">
         <v>19.2</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="11" t="n">
         <v>57.19</v>
       </c>
       <c r="F34" s="3" t="n">
@@ -3331,7 +3334,7 @@
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
+      <c r="M34" s="12" t="inlineStr"/>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
@@ -3341,10 +3344,10 @@
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3356,10 +3359,10 @@
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="14" t="n">
+      <c r="V34" s="10" t="n">
         <v>16.9</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="10" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3424,10 +3427,10 @@
       <c r="P35" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="14" t="n">
@@ -3439,10 +3442,10 @@
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="14" t="n">
+      <c r="V35" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3497,7 +3500,7 @@
       <c r="L36" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="11" t="n">
         <v>1.9</v>
       </c>
       <c r="N36" s="14" t="n">
@@ -3509,10 +3512,10 @@
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3524,10 +3527,10 @@
       <c r="U36" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3576,13 +3579,13 @@
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="15" t="n">
         <v>50.7</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="15" t="n">
         <v>68.5</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="15" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3594,10 +3597,10 @@
       <c r="P37" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="10" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3609,10 +3612,10 @@
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="10" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3664,10 +3667,10 @@
       <c r="K38" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L38" s="14" t="n">
+      <c r="L38" s="15" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="14" t="n">
+      <c r="M38" s="15" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3679,10 +3682,10 @@
       <c r="P38" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="15" t="n">
         <v>17</v>
       </c>
       <c r="S38" s="14" t="n">
@@ -3694,10 +3697,10 @@
       <c r="U38" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V38" s="14" t="n">
+      <c r="V38" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="10" t="n">
         <v>16.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3749,10 +3752,10 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="11" t="n">
         <v>1.2</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3782,7 +3785,7 @@
       <c r="V39" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W39" s="14" t="n">
+      <c r="W39" s="11" t="n">
         <v>62.5</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3935,7 +3938,7 @@
       <c r="Q41" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="14" t="n">
+      <c r="R41" s="11" t="n">
         <v>72.2</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3947,8 +3950,8 @@
       <c r="U41" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V41" s="14" t="n">
-        <v>641.7</v>
+      <c r="V41" s="11" t="n">
+        <v>64.17</v>
       </c>
       <c r="W41" s="14" t="n">
         <v>16.2</v>
@@ -4002,7 +4005,7 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="11" t="n">
         <v>4.6</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -4017,7 +4020,7 @@
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="14" t="n">
+      <c r="Q42" s="11" t="n">
         <v>61.7</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4072,7 +4075,7 @@
       <c r="F43" s="10" t="n">
         <v>19.2</v>
       </c>
-      <c r="G43" s="16" t="n">
+      <c r="G43" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4090,8 +4093,8 @@
       <c r="L43" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="M43" s="14" t="n">
-        <v>122.7</v>
+      <c r="M43" s="11" t="n">
+        <v>12.27</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>19.9</v>
@@ -4149,25 +4152,25 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="10" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="12" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4208,13 +4211,13 @@
       <c r="J45" s="3" t="n">
         <v>127.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="15" t="n">
         <v>36.4</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="15" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4226,10 +4229,10 @@
       <c r="P45" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="15" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="15" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4241,10 +4244,10 @@
       <c r="U45" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="15" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="15" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4275,13 +4278,13 @@
       <c r="D46" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="11" t="n">
         <v>101.4</v>
       </c>
       <c r="F46" s="15" t="n">
         <v>31.5</v>
       </c>
-      <c r="G46" s="16" t="n">
+      <c r="G46" s="11" t="n">
         <v>101.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4296,10 +4299,10 @@
       <c r="K46" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L46" s="14" t="n">
+      <c r="L46" s="15" t="n">
         <v>1213.8</v>
       </c>
-      <c r="M46" s="14" t="n">
+      <c r="M46" s="15" t="n">
         <v>101.9</v>
       </c>
       <c r="N46" s="14" t="n">
@@ -4311,10 +4314,10 @@
       <c r="P46" s="14" t="n">
         <v>24.1</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="15" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="14" t="n">
+      <c r="R46" s="15" t="n">
         <v>12.8</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4326,10 +4329,10 @@
       <c r="U46" s="14" t="n">
         <v>365.4</v>
       </c>
-      <c r="V46" s="14" t="n">
+      <c r="V46" s="15" t="n">
         <v>1841.6</v>
       </c>
-      <c r="W46" s="3" t="inlineStr"/>
+      <c r="W46" s="13" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -61,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,10 +146,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,16 +164,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,20 +783,20 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>11</v>
+      <c r="H4" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>11</v>
@@ -813,40 +807,40 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="14" t="n">
+      <c r="L4" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="13" t="n">
         <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -856,7 +850,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -872,21 +866,21 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>14649.5</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F5" s="10" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="11" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -908,19 +902,19 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -928,20 +922,20 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="10" t="n">
-        <v>17.9</v>
+      <c r="W5" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -959,23 +953,23 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="D6" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H6" s="11" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>1.7</v>
@@ -983,14 +977,14 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N6" s="14" t="n">
-        <v>256.1</v>
+      <c r="L6" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
@@ -999,11 +993,11 @@
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>62.5</v>
@@ -1011,20 +1005,20 @@
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="9" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1040,18 +1034,18 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>353.7</v>
-      </c>
-      <c r="D7" s="10" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="9" t="n">
         <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1076,7 +1070,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>8.4</v>
@@ -1084,32 +1078,32 @@
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="10" t="n">
-        <v>17.2</v>
+      <c r="R7" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>7.7</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="10" t="n">
+      <c r="V7" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="10" t="n">
+      <c r="W7" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.5</v>
+        <v>33.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1127,17 +1121,17 @@
       <c r="C8" s="3" t="n">
         <v>377.9</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1154,14 +1148,14 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="11" t="n">
         <v>13.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>12.1</v>
+        <v>17.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>4.1</v>
+        <v>9.9</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1169,22 +1163,22 @@
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1210,18 +1204,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1825.2</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>126.5</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>71.5</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="9" t="n">
         <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1230,54 +1224,56 @@
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="15" t="n">
+      <c r="J9" s="3" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="15" t="n">
+      <c r="L9" s="12" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="15" t="n">
-        <v>8.199999999999999</v>
+      <c r="M9" s="12" t="n">
+        <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>422</v>
+        <v>95.3</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="Q9" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q9" s="12" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="12" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>9285.6</v>
+        <v>198.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.1</v>
+        <v>891.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="W9" s="15" t="n">
-        <v>871.2</v>
+      <c r="V9" s="12" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="W9" s="9" t="n">
+        <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429.799999999999</v>
+        <v>9429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>116.9</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1293,19 +1289,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3650.1</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>11.8</v>
+      <c r="G10" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>12.3</v>
@@ -1317,42 +1313,42 @@
         <v>11.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="15" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M10" s="15" t="n">
-        <v>19.2</v>
+        <v>1.1</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>14.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q10" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q10" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="R10" s="12" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="V10" s="10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="W10" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <v>191.4</v>
+      </c>
+      <c r="W10" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1378,16 +1374,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>329.6</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13.3</v>
+        <v>324.6</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>55.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1399,55 +1395,55 @@
         <v>0.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>231.6</v>
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>13.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>91.8</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="13" t="n">
         <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="S11" s="14" t="n">
-        <v>89.90000000000001</v>
+      <c r="S11" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>72</v>
+        <v>1220.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V11" s="10" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="W11" s="14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="W11" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X11" s="14" t="n">
-        <v>18.4</v>
-      </c>
       <c r="Y11" s="3" t="n">
-        <v>98.8</v>
+        <v>93.8</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1463,74 +1459,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>501.1</v>
-      </c>
-      <c r="D12" s="10" t="n">
+        <v>511.1</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>110</v>
+      <c r="H12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>3.7</v>
+      </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>14.9</v>
+      <c r="L12" s="9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>24.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.2</v>
+        <v>16.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="R12" s="11" t="n">
-        <v>2.5</v>
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>12.9</v>
+        <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="14" t="n">
+      <c r="W12" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>89</v>
+        <v>281</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1546,19 +1544,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>155.6</v>
-      </c>
-      <c r="D13" s="3" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1570,49 +1568,49 @@
         <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
+        <v>98.2</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="S13" s="14" t="n">
-        <v>29.7</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>66.8</v>
+        <v>1866.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>26</v>
+        <v>726</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1631,18 +1629,18 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F14" s="10" t="n">
+      <c r="E14" s="9" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1657,20 +1655,20 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N14" s="14" t="n">
-        <v>94.3</v>
+        <v>12.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1682,22 +1680,22 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>171.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="V14" s="10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V14" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>18.9</v>
+      <c r="W14" s="9" t="n">
+        <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>86.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1716,43 +1714,43 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>454.5</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E15" s="10" t="n">
+        <v>484.5</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>13.6</v>
+      <c r="G15" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.2</v>
+        <v>10.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.2</v>
+        <v>13.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L15" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M15" s="11" t="n">
         <v>14.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1767,25 +1765,25 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>248</v>
+        <v>48</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>1.8</v>
+        <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>31.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1803,17 +1801,17 @@
       <c r="C16" s="3" t="n">
         <v>2306.9</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="9" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="15" t="n">
-        <v>655.3</v>
-      </c>
-      <c r="F16" s="15" t="n">
+      <c r="E16" s="12" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>95.7</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>62</v>
+      <c r="G16" s="13" t="n">
+        <v>16.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1822,30 +1820,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>134.9</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L16" s="15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="15" t="n">
-        <v>6.8</v>
+      <c r="M16" s="12" t="n">
+        <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>493</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q16" s="15" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="R16" s="15" t="n">
+        <v>432</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="12" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1855,19 +1851,19 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="V16" s="15" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="W16" s="15" t="n">
-        <v>90.90000000000001</v>
+        <v>255.8</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="W16" s="12" t="n">
+        <v>190.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9421</v>
+        <v>921</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>118.4</v>
@@ -1886,19 +1882,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>814.1</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>461.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>12.4</v>
+      <c r="E17" s="9" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>11.2</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1907,31 +1903,31 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="15" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M17" s="15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M17" s="12" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="15" t="n">
-        <v>11.8</v>
+      <c r="R17" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>18.3</v>
@@ -1939,13 +1935,13 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V17" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="W17" s="15" t="n">
+      <c r="U17" s="11" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1955,7 +1951,7 @@
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1971,26 +1967,28 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>955.7</v>
-      </c>
-      <c r="D18" s="10" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="J18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.3</v>
@@ -1998,37 +1996,37 @@
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="14" t="n">
-        <v>18</v>
+      <c r="M18" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>982.8</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q18" s="11" t="n">
-        <v>21.68</v>
-      </c>
-      <c r="R18" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="R18" s="9" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V18" s="14" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="W18" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2056,68 +2054,68 @@
       <c r="C19" s="3" t="n">
         <v>435.6</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H19" s="3" t="n">
+      <c r="D19" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H19" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>21.8</v>
+      <c r="M19" s="11" t="n">
+        <v>11.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.8</v>
+        <v>47</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="R19" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R19" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>12.4</v>
+      <c r="S19" s="11" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
       </c>
-      <c r="U19" s="14" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="V19" s="14" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W19" s="10" t="n">
+      <c r="U19" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="W19" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="X19" s="14" t="n">
-        <v>88.90000000000001</v>
+      <c r="X19" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>84</v>
@@ -2139,18 +2137,18 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1497.9</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F20" s="14" t="n">
+        <v>1417.9</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2171,42 +2169,44 @@
       <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>184.4</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="14" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R20" s="10" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="R20" s="9" t="n">
         <v>17.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V20" s="11" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="W20" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2222,40 +2222,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>371.3</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E21" s="10" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E21" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>15.6</v>
+      <c r="G21" s="9" t="n">
+        <v>11.6</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>21.1</v>
+      <c r="K21" s="11" t="n">
+        <v>41.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="14" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N21" s="14" t="n">
-        <v>88.7</v>
+      <c r="M21" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
@@ -2266,8 +2266,8 @@
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>18.9</v>
+      <c r="R21" s="9" t="n">
+        <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>19.3</v>
@@ -2276,21 +2276,23 @@
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="10" t="n">
-        <v>16.9</v>
+      <c r="W21" s="9" t="n">
+        <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Z21" s="3" t="inlineStr"/>
+        <v>918.1</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2307,17 +2309,17 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="F22" s="14" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>19.8</v>
+      <c r="F22" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>12.7</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>10.6</v>
@@ -2331,44 +2333,44 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" s="11" t="n">
-        <v>12.09</v>
+      <c r="M22" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>97</v>
+        <v>297</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q22" s="11" t="n">
-        <v>22.46</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>18.54</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8.9</v>
+        <v>59.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="9" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
@@ -2392,70 +2394,72 @@
       <c r="C23" s="3" t="n">
         <v>2089.4</v>
       </c>
-      <c r="D23" s="15" t="n">
-        <v>1128.4</v>
-      </c>
-      <c r="E23" s="15" t="n">
+      <c r="D23" s="9" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>66.8</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="9" t="n">
         <v>97.5</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>69.40000000000001</v>
+      <c r="G23" s="9" t="n">
+        <v>61.4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.9</v>
+        <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="K23" s="15" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="L23" s="15" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M23" s="15" t="n">
+      <c r="K23" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>71.8</v>
+        <v>7.9</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="15" t="n">
+      <c r="P23" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q23" s="12" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="15" t="n">
-        <v>918.5</v>
+      <c r="R23" s="12" t="n">
+        <v>191.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>3260.6</v>
+        <v>232.8</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="V23" s="15" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="V23" s="12" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="15" t="n">
+      <c r="W23" s="9" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>93.8</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>198.3</v>
+        <v>116.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2471,64 +2475,64 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4912.9</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F24" s="10" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F24" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="14" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>10.5</v>
+      <c r="G24" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>37.1</v>
+        <v>13.7</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" s="15" t="n">
+      <c r="L24" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P24" s="14" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Q24" s="15" t="n">
+      <c r="P24" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="15" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="W24" s="10" t="n">
+      <c r="V24" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W24" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2538,7 +2542,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>3.8</v>
+        <v>128.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2554,49 +2558,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>223.6</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H25" s="14" t="n">
+      <c r="G25" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H25" s="11" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.2</v>
+        <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="O25" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>18.4</v>
+      <c r="Q25" s="13" t="n">
+        <v>0.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2608,22 +2612,22 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="V25" s="11" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="W25" s="11" t="n">
-        <v>0.1</v>
+        <v>27.9</v>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>12.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>920.8</v>
+        <v>92</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>12.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2639,56 +2643,58 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>268.3</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F26" s="10" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>7.7</v>
+      <c r="G26" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="14" t="n">
+      <c r="M26" s="11" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2.2</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>908.8</v>
+        <v>108</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Q26" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S26" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="S26" s="11" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2696,17 +2702,15 @@
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="14" t="n">
+      <c r="W26" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="X26" s="14" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2722,25 +2726,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>435.8</v>
-      </c>
-      <c r="D27" s="10" t="n">
+        <v>435.6</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>13.1</v>
+        <v>12.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2748,14 +2752,14 @@
       <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M27" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N27" s="14" t="n">
-        <v>8.800000000000001</v>
+      <c r="L27" s="13" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2763,7 +2767,7 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2772,14 +2776,16 @@
       <c r="S27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="T27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2807,23 +2813,23 @@
       <c r="C28" s="3" t="n">
         <v>331.3</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G28" s="10" t="n">
+      <c r="F28" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G28" s="9" t="n">
         <v>9.9</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.3</v>
@@ -2835,36 +2841,36 @@
         <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="14" t="n">
+      <c r="R28" s="11" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>1.8</v>
+        <v>48.1</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="14" t="n">
+      <c r="W28" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2890,19 +2896,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.1</v>
-      </c>
-      <c r="D29" s="3" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="D29" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="n">
+      <c r="E29" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H29" s="11" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2915,43 +2923,43 @@
         <v>0.6</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M29" s="14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M29" s="11" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q29" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="14" t="n">
+      <c r="R29" s="11" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.4</v>
+        <v>1.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="W29" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>17.9</v>
+      <c r="V29" s="11" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="W29" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X29" s="11" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>9.699999999999999</v>
@@ -2973,53 +2981,53 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1569.9</v>
-      </c>
-      <c r="D30" s="10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D30" s="9" t="n">
         <v>116.8</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="9" t="n">
         <v>94.3</v>
       </c>
-      <c r="G30" s="11" t="n">
-        <v>64.59999999999999</v>
+      <c r="G30" s="9" t="n">
+        <v>44.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K30" s="15" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="L30" s="15" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="M30" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>69</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>491.8</v>
+        <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="15" t="n">
+      <c r="Q30" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="12" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>413.1</v>
@@ -3027,20 +3035,20 @@
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="15" t="n">
+      <c r="V30" s="12" t="n">
         <v>8.5</v>
       </c>
-      <c r="W30" s="15" t="n">
-        <v>824.9</v>
+      <c r="W30" s="9" t="n">
+        <v>82.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>94228</v>
+        <v>9428</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3058,13 +3066,13 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3073,53 +3081,57 @@
       <c r="H31" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" s="14" t="n">
-        <v>81.5</v>
+      <c r="I31" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L31" s="15" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="15" t="n">
+      <c r="M31" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q31" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="n">
-        <v>1644.1</v>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="R31" s="15" t="n">
-        <v>17.8</v>
+      <c r="R31" s="12" t="n">
+        <v>87.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>9211.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W31" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="W31" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="X31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.1</v>
+        <v>16.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3137,38 +3149,38 @@
       <c r="C32" s="3" t="n">
         <v>364.2</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>31</v>
+      <c r="D32" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>31.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="L32" s="14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>27.5</v>
+        <v>39.1</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>9</v>
@@ -3176,35 +3188,31 @@
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q32" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="R32" s="10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="Q32" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="U32" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V32" s="10" t="n">
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3222,38 +3230,38 @@
       <c r="C33" s="3" t="n">
         <v>411.2</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="14" t="n">
+      <c r="H33" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="11" t="n">
-        <v>1.5</v>
+      <c r="L33" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="N33" s="14" t="n">
-        <v>60.1</v>
+        <v>17.2</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>9161.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3261,35 +3269,35 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>71.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V33" s="10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>2880.9</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.1</v>
+        <v>12.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3307,69 +3315,71 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="14" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>57.19</v>
+      <c r="D34" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H34" s="14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
+      <c r="M34" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R34" s="10" t="n">
+      <c r="Q34" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="R34" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>1.7</v>
+        <v>97.5</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="10" t="n">
+      <c r="V34" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="W34" s="10" t="n">
+      <c r="W34" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>8</v>
@@ -3388,21 +3398,21 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>172.8</v>
-      </c>
-      <c r="D35" s="10" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="E35" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F35" s="10" t="n">
+      <c r="E35" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F35" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3417,45 +3427,47 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="11" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="O35" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q35" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q35" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="10" t="n">
+      <c r="R35" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="S35" s="14" t="n">
-        <v>15.9</v>
+      <c r="S35" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>68.8</v>
+        <v>60.8</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="10" t="n">
+      <c r="V35" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W35" s="10" t="n">
+      <c r="W35" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1.7</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8.4</v>
+        <v>128.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3473,20 +3485,20 @@
       <c r="C36" s="3" t="n">
         <v>613.2</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G36" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>10.9</v>
+      <c r="G36" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3497,50 +3509,50 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="14" t="n">
+      <c r="L36" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N36" s="14" t="n">
-        <v>66.40000000000001</v>
+      <c r="M36" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>870.8</v>
+        <v>87</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="R36" s="10" t="n">
+      <c r="Q36" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V36" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="10" t="n">
+      <c r="W36" s="9" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>26.8</v>
+        <v>114.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3558,75 +3570,73 @@
       <c r="C37" s="3" t="n">
         <v>2078.2</v>
       </c>
-      <c r="D37" s="15" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>32.3</v>
+      <c r="D37" s="12" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>35.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>181.4</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="K37" s="15" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="L37" s="15" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="M37" s="15" t="n">
-        <v>67.59999999999999</v>
+        <v>12.1</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>507.9</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.1</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q37" s="15" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Q37" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>89.90000000000001</v>
+      <c r="R37" s="12" t="n">
+        <v>59.9</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3801.9</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="W37" s="10" t="n">
+      <c r="V37" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="W37" s="9" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>422.2</v>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v>19.6</v>
-      </c>
+        <v>429.8</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3643,74 +3653,74 @@
       <c r="C38" s="3" t="n">
         <v>415.6</v>
       </c>
-      <c r="D38" s="15" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F38" s="15" t="n">
+      <c r="D38" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G38" s="14" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>170.2</v>
+      <c r="G38" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>17</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.4</v>
+        <v>12.9</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L38" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="15" t="n">
+      <c r="M38" s="12" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>41.4</v>
+        <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q38" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Q38" s="12" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="S38" s="14" t="n">
+      <c r="R38" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V38" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="3" t="n">
+      <c r="X38" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3726,40 +3736,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.4</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E39" s="10" t="n">
+        <v>624.3</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G39" s="10" t="n">
+      <c r="F39" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M39" s="11" t="n">
+      <c r="L39" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M39" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
@@ -3767,14 +3777,14 @@
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>14.8</v>
+      <c r="Q39" s="9" t="n">
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.8</v>
+        <v>0.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3782,20 +3792,20 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>62.5</v>
+      <c r="V39" s="13" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>16.5</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>61</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3813,20 +3823,20 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F40" s="10" t="n">
+      <c r="D40" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>11.6</v>
+      <c r="G40" s="11" t="n">
+        <v>65.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.3</v>
+        <v>15.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
@@ -3850,27 +3860,27 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q40" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q40" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.9</v>
+        <v>1948.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="W40" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3880,7 +3890,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3896,74 +3906,72 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>699.3</v>
-      </c>
-      <c r="D41" s="10" t="n">
+        <v>644.3</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G41" s="3" t="n">
+      <c r="E41" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="14" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>1.2</v>
+      <c r="L41" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>18.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="11" t="n">
-        <v>72.2</v>
+      <c r="R41" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>97</v>
+        <v>947</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V41" s="11" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="W41" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W41" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>1.5</v>
+      <c r="X41" s="11" t="n">
+        <v>88.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39</v>
+        <v>239</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>22.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3981,74 +3989,72 @@
       <c r="C42" s="3" t="n">
         <v>608.8</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>18.6</v>
+      <c r="E42" s="13" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>31.7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1.6</v>
+        <v>16.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.1</v>
+        <v>10</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="11" t="n">
-        <v>61.7</v>
+      <c r="Q42" s="9" t="n">
+        <v>26.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>14.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4064,19 +4070,19 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5049.4</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F43" s="10" t="n">
+        <v>604.4</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="G43" s="11" t="n">
-        <v>12.8</v>
+      <c r="G43" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>8</v>
@@ -4090,50 +4096,50 @@
       <c r="K43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="14" t="n">
-        <v>13</v>
+      <c r="L43" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>19.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q43" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>16.5</v>
+        <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W43" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V43" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W43" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>12.1</v>
+      <c r="X43" s="11" t="n">
+        <v>120.9</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>39.8</v>
+        <v>239.2</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>210.9</v>
+        <v>113</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4151,26 +4157,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="10" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="12" t="inlineStr"/>
-      <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr"/>
+      <c r="M44" s="15" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
-      <c r="R44" s="12" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="R44" s="15" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="inlineStr"/>
-      <c r="W44" s="12" t="inlineStr"/>
+      <c r="V44" s="15" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4190,17 +4196,17 @@
       <c r="C45" s="3" t="n">
         <v>3119.5</v>
       </c>
-      <c r="D45" s="15" t="n">
-        <v>131.9</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="F45" s="15" t="n">
+      <c r="D45" s="9" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>77.5</v>
+      <c r="G45" s="9" t="n">
+        <v>77.2</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
@@ -4209,52 +4215,52 @@
         <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="K45" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="15" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="M45" s="15" t="n">
-        <v>55.9</v>
+        <v>23.2</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>155.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>61.9</v>
+        <v>161.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>298</v>
+        <v>9498</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q45" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="12" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="15" t="n">
+      <c r="R45" s="12" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>81.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2172.5</v>
+        <v>282.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V45" s="15" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V45" s="12" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="15" t="n">
-        <v>88.09999999999999</v>
+      <c r="W45" s="12" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>10688.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>302.8</v>
+        <v>2302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>20.7</v>
@@ -4275,17 +4281,17 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="11" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>31.5</v>
+      <c r="E46" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>18.5</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>101.5</v>
+        <v>51.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4294,53 +4300,53 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L46" s="15" t="n">
-        <v>1213.8</v>
-      </c>
-      <c r="M46" s="15" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="N46" s="14" t="n">
-        <v>32.1</v>
+        <v>15.5</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="12" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P46" s="14" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="Q46" s="15" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q46" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="15" t="n">
-        <v>12.8</v>
+      <c r="R46" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.6</v>
+        <v>11.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="U46" s="14" t="n">
-        <v>365.4</v>
-      </c>
-      <c r="V46" s="15" t="n">
-        <v>1841.6</v>
-      </c>
-      <c r="W46" s="13" t="inlineStr"/>
+        <v>58.5</v>
+      </c>
+      <c r="U46" s="11" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="9" t="n">
+        <v>16.6</v>
+      </c>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>21.8</v>
+        <v>161.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>18.1</v>
+        <v>885.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1223,7 +1223,7 @@
       <c r="J9" s="3" t="n">
         <v>1128.9</v>
       </c>
-      <c r="K9" s="3" t="n"/>
+      <c r="K9" s="13" t="n"/>
       <c r="L9" s="3" t="n">
         <v>74.90000000000001</v>
       </c>
@@ -1360,8 +1360,8 @@
       <c r="C11" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="16" t="n">
         <v>1.6</v>
       </c>
@@ -1377,7 +1377,7 @@
       <c r="J11" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="14" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n">
         <v>14.9</v>
@@ -1436,7 +1436,7 @@
       <c r="D12" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="E12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="F12" s="16" t="n">
         <v>0</v>
       </c>
@@ -1450,7 +1450,7 @@
       <c r="J12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K12" s="3" t="n"/>
+      <c r="K12" s="14" t="n"/>
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
@@ -1774,7 +1774,7 @@
       <c r="J16" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="17" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -1938,7 +1938,7 @@
       <c r="J18" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="11" t="n">
         <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -2013,7 +2013,7 @@
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -2090,7 +2090,7 @@
       <c r="J20" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -2171,7 +2171,7 @@
       <c r="J21" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
@@ -2254,7 +2254,7 @@
       <c r="J22" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="L22" s="3" t="n">
@@ -2337,7 +2337,7 @@
       <c r="J23" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2874,7 +2874,7 @@
       <c r="C30" s="3" t="n">
         <v>1116.8</v>
       </c>
-      <c r="D30" s="14" t="n"/>
+      <c r="D30" s="13" t="n"/>
       <c r="E30" s="17" t="n">
         <v>14</v>
       </c>
@@ -2893,7 +2893,7 @@
       <c r="J30" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" s="3" t="n"/>
+      <c r="K30" s="13" t="n"/>
       <c r="L30" s="3" t="n">
         <v>13.7</v>
       </c>
@@ -3058,7 +3058,7 @@
       <c r="J32" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="14" t="n"/>
       <c r="L32" s="3" t="n">
         <v>15</v>
       </c>
@@ -3461,7 +3461,7 @@
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="17" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -3524,7 +3524,7 @@
       <c r="D38" s="16" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="14" t="n"/>
+      <c r="E38" s="13" t="n"/>
       <c r="F38" s="16" t="n">
         <v>92.2</v>
       </c>
@@ -3854,7 +3854,7 @@
       <c r="D42" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="E42" s="13" t="n"/>
+      <c r="E42" s="14" t="n"/>
       <c r="F42" s="3" t="n">
         <v>18.7</v>
       </c>
@@ -4131,7 +4131,7 @@
       <c r="J45" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="17" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
